--- a/data/raw/MGLU3.SA.xlsx
+++ b/data/raw/MGLU3.SA.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F252"/>
+  <dimension ref="A1:F251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,5022 +468,5002 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45833</v>
+        <v>45845</v>
       </c>
       <c r="B2" t="n">
-        <v>8.614230155944824</v>
+        <v>8.595359802246094</v>
       </c>
       <c r="C2" t="n">
-        <v>8.699145950613564</v>
+        <v>8.793496339880617</v>
       </c>
       <c r="D2" t="n">
-        <v>8.491573798136745</v>
+        <v>8.491573726878618</v>
       </c>
       <c r="E2" t="n">
-        <v>8.633099492724948</v>
+        <v>8.708580545924459</v>
       </c>
       <c r="F2" t="n">
-        <v>24805620</v>
+        <v>17286990</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45834</v>
+        <v>45846</v>
       </c>
       <c r="B3" t="n">
-        <v>8.887846946716309</v>
+        <v>8.397222518920898</v>
       </c>
       <c r="C3" t="n">
-        <v>8.991633023771955</v>
+        <v>8.736885702798975</v>
       </c>
       <c r="D3" t="n">
-        <v>8.661405455676308</v>
+        <v>8.312307667740939</v>
       </c>
       <c r="E3" t="n">
-        <v>8.802931151378921</v>
+        <v>8.651969906829455</v>
       </c>
       <c r="F3" t="n">
-        <v>28136850</v>
+        <v>22664355</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45835</v>
+        <v>45847</v>
       </c>
       <c r="B4" t="n">
-        <v>8.774625778198242</v>
+        <v>8.066994667053223</v>
       </c>
       <c r="C4" t="n">
-        <v>8.906716799068795</v>
+        <v>8.491573632094822</v>
       </c>
       <c r="D4" t="n">
-        <v>8.633099144528646</v>
+        <v>8.000949155245587</v>
       </c>
       <c r="E4" t="n">
-        <v>8.802930727016358</v>
+        <v>8.491573632094822</v>
       </c>
       <c r="F4" t="n">
-        <v>22057560</v>
+        <v>20102670</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45838</v>
+        <v>45848</v>
       </c>
       <c r="B5" t="n">
-        <v>9.29355525970459</v>
+        <v>7.868857860565186</v>
       </c>
       <c r="C5" t="n">
-        <v>9.397341332494458</v>
+        <v>7.934903370097695</v>
       </c>
       <c r="D5" t="n">
-        <v>8.680274435831462</v>
+        <v>7.670721331967656</v>
       </c>
       <c r="E5" t="n">
-        <v>8.727449665793353</v>
+        <v>7.774507402601455</v>
       </c>
       <c r="F5" t="n">
-        <v>37561860</v>
+        <v>27701730</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45839</v>
+        <v>45849</v>
       </c>
       <c r="B6" t="n">
-        <v>9.161464691162109</v>
+        <v>7.585805416107178</v>
       </c>
       <c r="C6" t="n">
-        <v>9.369035902221992</v>
+        <v>7.774507757841235</v>
       </c>
       <c r="D6" t="n">
-        <v>9.029373662817759</v>
+        <v>7.472585144814188</v>
       </c>
       <c r="E6" t="n">
-        <v>9.218074592001368</v>
+        <v>7.774507757841235</v>
       </c>
       <c r="F6" t="n">
-        <v>18460050</v>
+        <v>25093320</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45840</v>
+        <v>45852</v>
       </c>
       <c r="B7" t="n">
-        <v>8.557619094848633</v>
+        <v>7.500889301300049</v>
       </c>
       <c r="C7" t="n">
-        <v>9.236944490231648</v>
+        <v>7.557500143117218</v>
       </c>
       <c r="D7" t="n">
-        <v>8.519879477453118</v>
+        <v>7.368798754244233</v>
       </c>
       <c r="E7" t="n">
-        <v>9.180334591743618</v>
+        <v>7.557500143117218</v>
       </c>
       <c r="F7" t="n">
-        <v>26958645</v>
+        <v>19896135</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45841</v>
+        <v>45853</v>
       </c>
       <c r="B8" t="n">
-        <v>8.670840263366699</v>
+        <v>7.595240592956543</v>
       </c>
       <c r="C8" t="n">
-        <v>8.859542138789685</v>
+        <v>7.774507794837225</v>
       </c>
       <c r="D8" t="n">
-        <v>8.604794748687089</v>
+        <v>7.482019376335239</v>
       </c>
       <c r="E8" t="n">
-        <v>8.765191673472975</v>
+        <v>7.736766759437096</v>
       </c>
       <c r="F8" t="n">
-        <v>26035695</v>
+        <v>24724665</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45842</v>
+        <v>45854</v>
       </c>
       <c r="B9" t="n">
-        <v>8.727449417114258</v>
+        <v>7.651850700378418</v>
       </c>
       <c r="C9" t="n">
-        <v>8.736885029711486</v>
+        <v>7.708461542928184</v>
       </c>
       <c r="D9" t="n">
-        <v>8.585923731261202</v>
+        <v>7.425409219758372</v>
       </c>
       <c r="E9" t="n">
-        <v>8.585923731261202</v>
+        <v>7.604675470648368</v>
       </c>
       <c r="F9" t="n">
-        <v>16310595</v>
+        <v>21844725</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45845</v>
+        <v>45855</v>
       </c>
       <c r="B10" t="n">
-        <v>8.595359802246094</v>
+        <v>7.736766815185547</v>
       </c>
       <c r="C10" t="n">
-        <v>8.793496339880617</v>
+        <v>7.765072710038298</v>
       </c>
       <c r="D10" t="n">
-        <v>8.491573726878618</v>
+        <v>7.566935697622002</v>
       </c>
       <c r="E10" t="n">
-        <v>8.708580545924459</v>
+        <v>7.680155970269591</v>
       </c>
       <c r="F10" t="n">
-        <v>17286990</v>
+        <v>22185345</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45846</v>
+        <v>45856</v>
       </c>
       <c r="B11" t="n">
-        <v>8.397222518920898</v>
+        <v>7.434844017028809</v>
       </c>
       <c r="C11" t="n">
-        <v>8.736885702798975</v>
+        <v>7.680155782763043</v>
       </c>
       <c r="D11" t="n">
-        <v>8.312307667740939</v>
+        <v>7.387668314083946</v>
       </c>
       <c r="E11" t="n">
-        <v>8.651969906829455</v>
+        <v>7.595240462251815</v>
       </c>
       <c r="F11" t="n">
-        <v>22664355</v>
+        <v>24625335</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45847</v>
+        <v>45859</v>
       </c>
       <c r="B12" t="n">
-        <v>8.066994667053223</v>
+        <v>7.170661926269531</v>
       </c>
       <c r="C12" t="n">
-        <v>8.491573632094822</v>
+        <v>7.529195376879078</v>
       </c>
       <c r="D12" t="n">
-        <v>8.000949155245587</v>
+        <v>7.161226785738253</v>
       </c>
       <c r="E12" t="n">
-        <v>8.491573632094822</v>
+        <v>7.491454342359204</v>
       </c>
       <c r="F12" t="n">
-        <v>20102670</v>
+        <v>21647010</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45848</v>
+        <v>45860</v>
       </c>
       <c r="B13" t="n">
-        <v>7.868857860565186</v>
+        <v>7.076311588287354</v>
       </c>
       <c r="C13" t="n">
-        <v>7.934903370097695</v>
+        <v>7.283882321596203</v>
       </c>
       <c r="D13" t="n">
-        <v>7.670721331967656</v>
+        <v>7.000830462730012</v>
       </c>
       <c r="E13" t="n">
-        <v>7.774507402601455</v>
+        <v>7.227272894612501</v>
       </c>
       <c r="F13" t="n">
-        <v>27701730</v>
+        <v>22623300</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45849</v>
+        <v>45861</v>
       </c>
       <c r="B14" t="n">
-        <v>7.585805416107178</v>
+        <v>7.359364032745361</v>
       </c>
       <c r="C14" t="n">
-        <v>7.774507757841235</v>
+        <v>7.453714496353741</v>
       </c>
       <c r="D14" t="n">
-        <v>7.472585144814188</v>
+        <v>6.972525620287723</v>
       </c>
       <c r="E14" t="n">
-        <v>7.774507757841235</v>
+        <v>7.010265711252121</v>
       </c>
       <c r="F14" t="n">
-        <v>25093320</v>
+        <v>20511330</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45852</v>
+        <v>45862</v>
       </c>
       <c r="B15" t="n">
-        <v>7.500889301300049</v>
+        <v>7.114051342010498</v>
       </c>
       <c r="C15" t="n">
-        <v>7.557500143117218</v>
+        <v>7.293317589541401</v>
       </c>
       <c r="D15" t="n">
-        <v>7.368798754244233</v>
+        <v>7.048005360273342</v>
       </c>
       <c r="E15" t="n">
-        <v>7.557500143117218</v>
+        <v>7.26501264119165</v>
       </c>
       <c r="F15" t="n">
-        <v>19896135</v>
+        <v>16325925</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45853</v>
+        <v>45863</v>
       </c>
       <c r="B16" t="n">
-        <v>7.595240592956543</v>
+        <v>7.076311588287354</v>
       </c>
       <c r="C16" t="n">
-        <v>7.774507794837225</v>
+        <v>7.161226909749827</v>
       </c>
       <c r="D16" t="n">
-        <v>7.482019376335239</v>
+        <v>6.925350281962206</v>
       </c>
       <c r="E16" t="n">
-        <v>7.736766759437096</v>
+        <v>7.114051678671256</v>
       </c>
       <c r="F16" t="n">
-        <v>24724665</v>
+        <v>16280145</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45854</v>
+        <v>45866</v>
       </c>
       <c r="B17" t="n">
-        <v>7.651850700378418</v>
+        <v>6.774388790130615</v>
       </c>
       <c r="C17" t="n">
-        <v>7.708461542928184</v>
+        <v>7.123486624299962</v>
       </c>
       <c r="D17" t="n">
-        <v>7.425409219758372</v>
+        <v>6.76495317729956</v>
       </c>
       <c r="E17" t="n">
-        <v>7.604675470648368</v>
+        <v>7.057440641245858</v>
       </c>
       <c r="F17" t="n">
-        <v>21844725</v>
+        <v>16992360</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45855</v>
+        <v>45867</v>
       </c>
       <c r="B18" t="n">
-        <v>7.736766815185547</v>
+        <v>6.585687160491943</v>
       </c>
       <c r="C18" t="n">
-        <v>7.765072710038298</v>
+        <v>6.840433599361353</v>
       </c>
       <c r="D18" t="n">
-        <v>7.566935697622002</v>
+        <v>6.557381738176025</v>
       </c>
       <c r="E18" t="n">
-        <v>7.680155970269591</v>
+        <v>6.840433599361353</v>
       </c>
       <c r="F18" t="n">
-        <v>22185345</v>
+        <v>22201725</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45856</v>
+        <v>45868</v>
       </c>
       <c r="B19" t="n">
-        <v>7.434844017028809</v>
+        <v>6.925350189208984</v>
       </c>
       <c r="C19" t="n">
-        <v>7.680155782763043</v>
+        <v>7.057440739980902</v>
       </c>
       <c r="D19" t="n">
-        <v>7.387668314083946</v>
+        <v>6.529076647314187</v>
       </c>
       <c r="E19" t="n">
-        <v>7.595240462251815</v>
+        <v>6.547945983661265</v>
       </c>
       <c r="F19" t="n">
-        <v>24625335</v>
+        <v>29697360</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45859</v>
+        <v>45869</v>
       </c>
       <c r="B20" t="n">
-        <v>7.170661926269531</v>
+        <v>6.661167144775391</v>
       </c>
       <c r="C20" t="n">
-        <v>7.529195376879078</v>
+        <v>6.746082936815731</v>
       </c>
       <c r="D20" t="n">
-        <v>7.161226785738253</v>
+        <v>6.576251825129807</v>
       </c>
       <c r="E20" t="n">
-        <v>7.491454342359204</v>
+        <v>6.680037898155725</v>
       </c>
       <c r="F20" t="n">
-        <v>21647010</v>
+        <v>21455490</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45860</v>
+        <v>45870</v>
       </c>
       <c r="B21" t="n">
-        <v>7.076311588287354</v>
+        <v>6.812129020690918</v>
       </c>
       <c r="C21" t="n">
-        <v>7.283882321596203</v>
+        <v>6.981960607275288</v>
       </c>
       <c r="D21" t="n">
-        <v>7.000830462730012</v>
+        <v>6.774388930558149</v>
       </c>
       <c r="E21" t="n">
-        <v>7.227272894612501</v>
+        <v>6.85930425145557</v>
       </c>
       <c r="F21" t="n">
-        <v>22623300</v>
+        <v>26666745</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45861</v>
+        <v>45873</v>
       </c>
       <c r="B22" t="n">
-        <v>7.359364032745361</v>
+        <v>6.774388790130615</v>
       </c>
       <c r="C22" t="n">
-        <v>7.453714496353741</v>
+        <v>6.963090181672362</v>
       </c>
       <c r="D22" t="n">
-        <v>6.972525620287723</v>
+        <v>6.727213087949113</v>
       </c>
       <c r="E22" t="n">
-        <v>7.010265711252121</v>
+        <v>6.897044198618258</v>
       </c>
       <c r="F22" t="n">
-        <v>20511330</v>
+        <v>15100470</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45862</v>
+        <v>45874</v>
       </c>
       <c r="B23" t="n">
-        <v>7.114051342010498</v>
+        <v>6.793258190155029</v>
       </c>
       <c r="C23" t="n">
-        <v>7.293317589541401</v>
+        <v>6.887609123011355</v>
       </c>
       <c r="D23" t="n">
-        <v>7.048005360273342</v>
+        <v>6.698907257298704</v>
       </c>
       <c r="E23" t="n">
-        <v>7.26501264119165</v>
+        <v>6.774388853894331</v>
       </c>
       <c r="F23" t="n">
-        <v>16325925</v>
+        <v>15683955</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45863</v>
+        <v>45875</v>
       </c>
       <c r="B24" t="n">
-        <v>7.076311588287354</v>
+        <v>6.925350189208984</v>
       </c>
       <c r="C24" t="n">
-        <v>7.161226909749827</v>
+        <v>7.019700650102463</v>
       </c>
       <c r="D24" t="n">
-        <v>6.925350281962206</v>
+        <v>6.802693361821083</v>
       </c>
       <c r="E24" t="n">
-        <v>7.114051678671256</v>
+        <v>6.849869064662584</v>
       </c>
       <c r="F24" t="n">
-        <v>16280145</v>
+        <v>14000910</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45866</v>
+        <v>45876</v>
       </c>
       <c r="B25" t="n">
-        <v>6.774388790130615</v>
+        <v>7.000830173492432</v>
       </c>
       <c r="C25" t="n">
-        <v>7.123486624299962</v>
+        <v>7.057440542926827</v>
       </c>
       <c r="D25" t="n">
-        <v>6.76495317729956</v>
+        <v>6.868739154013928</v>
       </c>
       <c r="E25" t="n">
-        <v>7.057440641245858</v>
+        <v>6.953654471968146</v>
       </c>
       <c r="F25" t="n">
-        <v>16992360</v>
+        <v>18451335</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45867</v>
+        <v>45877</v>
       </c>
       <c r="B26" t="n">
-        <v>6.585687160491943</v>
+        <v>6.64229679107666</v>
       </c>
       <c r="C26" t="n">
-        <v>6.840433599361353</v>
+        <v>6.944219393961724</v>
       </c>
       <c r="D26" t="n">
-        <v>6.557381738176025</v>
+        <v>6.557381472360644</v>
       </c>
       <c r="E26" t="n">
-        <v>6.840433599361353</v>
+        <v>6.944219393961724</v>
       </c>
       <c r="F26" t="n">
-        <v>22201725</v>
+        <v>34780410</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45868</v>
+        <v>45880</v>
       </c>
       <c r="B27" t="n">
-        <v>6.925350189208984</v>
+        <v>6.623426914215088</v>
       </c>
       <c r="C27" t="n">
-        <v>7.057440739980902</v>
+        <v>6.953654462459799</v>
       </c>
       <c r="D27" t="n">
-        <v>6.529076647314187</v>
+        <v>6.547945791879442</v>
       </c>
       <c r="E27" t="n">
-        <v>6.547945983661265</v>
+        <v>6.547945791879442</v>
       </c>
       <c r="F27" t="n">
-        <v>29697360</v>
+        <v>28940520</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45869</v>
+        <v>45881</v>
       </c>
       <c r="B28" t="n">
-        <v>6.661167144775391</v>
+        <v>6.632862567901611</v>
       </c>
       <c r="C28" t="n">
-        <v>6.746082936815731</v>
+        <v>6.887608995385344</v>
       </c>
       <c r="D28" t="n">
-        <v>6.576251825129807</v>
+        <v>6.613991814806306</v>
       </c>
       <c r="E28" t="n">
-        <v>6.680037898155725</v>
+        <v>6.793258064277323</v>
       </c>
       <c r="F28" t="n">
-        <v>21455490</v>
+        <v>21292005</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45870</v>
+        <v>45882</v>
       </c>
       <c r="B29" t="n">
-        <v>6.812129020690918</v>
+        <v>6.349809646606445</v>
       </c>
       <c r="C29" t="n">
-        <v>6.981960607275288</v>
+        <v>6.651732264613072</v>
       </c>
       <c r="D29" t="n">
-        <v>6.774388930558149</v>
+        <v>6.321504696415059</v>
       </c>
       <c r="E29" t="n">
-        <v>6.85930425145557</v>
+        <v>6.613992173559632</v>
       </c>
       <c r="F29" t="n">
-        <v>26666745</v>
+        <v>21171150</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45873</v>
+        <v>45883</v>
       </c>
       <c r="B30" t="n">
-        <v>6.774388790130615</v>
+        <v>6.302634239196777</v>
       </c>
       <c r="C30" t="n">
-        <v>6.963090181672362</v>
+        <v>6.359244610398034</v>
       </c>
       <c r="D30" t="n">
-        <v>6.727213087949113</v>
+        <v>6.161108074996253</v>
       </c>
       <c r="E30" t="n">
-        <v>6.897044198618258</v>
+        <v>6.293198626202678</v>
       </c>
       <c r="F30" t="n">
-        <v>15100470</v>
+        <v>19710600</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45874</v>
+        <v>45884</v>
       </c>
       <c r="B31" t="n">
-        <v>6.793258190155029</v>
+        <v>6.246023178100586</v>
       </c>
       <c r="C31" t="n">
-        <v>6.887609123011355</v>
+        <v>6.302634019725293</v>
       </c>
       <c r="D31" t="n">
-        <v>6.698907257298704</v>
+        <v>6.151672720182234</v>
       </c>
       <c r="E31" t="n">
-        <v>6.774388853894331</v>
+        <v>6.28376421157847</v>
       </c>
       <c r="F31" t="n">
-        <v>15683955</v>
+        <v>13254045</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45875</v>
+        <v>45887</v>
       </c>
       <c r="B32" t="n">
-        <v>6.925350189208984</v>
+        <v>6.519641399383545</v>
       </c>
       <c r="C32" t="n">
-        <v>7.019700650102463</v>
+        <v>6.595121577897451</v>
       </c>
       <c r="D32" t="n">
-        <v>6.802693361821083</v>
+        <v>6.246023272198178</v>
       </c>
       <c r="E32" t="n">
-        <v>6.849869064662584</v>
+        <v>6.246023272198178</v>
       </c>
       <c r="F32" t="n">
-        <v>14000910</v>
+        <v>17826795</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45876</v>
+        <v>45888</v>
       </c>
       <c r="B33" t="n">
-        <v>7.000830173492432</v>
+        <v>6.472465991973877</v>
       </c>
       <c r="C33" t="n">
-        <v>7.057440542926827</v>
+        <v>6.547946173923972</v>
       </c>
       <c r="D33" t="n">
-        <v>6.868739154013928</v>
+        <v>6.340375437363824</v>
       </c>
       <c r="E33" t="n">
-        <v>6.953654471968146</v>
+        <v>6.359244774259185</v>
       </c>
       <c r="F33" t="n">
-        <v>18451335</v>
+        <v>17640105</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45877</v>
+        <v>45889</v>
       </c>
       <c r="B34" t="n">
-        <v>6.64229679107666</v>
+        <v>6.302634239196777</v>
       </c>
       <c r="C34" t="n">
-        <v>6.944219393961724</v>
+        <v>6.538511809390667</v>
       </c>
       <c r="D34" t="n">
-        <v>6.557381472360644</v>
+        <v>6.255458536200094</v>
       </c>
       <c r="E34" t="n">
-        <v>6.944219393961724</v>
+        <v>6.538511809390667</v>
       </c>
       <c r="F34" t="n">
-        <v>34780410</v>
+        <v>20240430</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45880</v>
+        <v>45890</v>
       </c>
       <c r="B35" t="n">
-        <v>6.623426914215088</v>
+        <v>6.302634239196777</v>
       </c>
       <c r="C35" t="n">
-        <v>6.953654462459799</v>
+        <v>6.48190143818941</v>
       </c>
       <c r="D35" t="n">
-        <v>6.547945791879442</v>
+        <v>6.246023395600758</v>
       </c>
       <c r="E35" t="n">
-        <v>6.547945791879442</v>
+        <v>6.264894149194194</v>
       </c>
       <c r="F35" t="n">
-        <v>28940520</v>
+        <v>15171030</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45881</v>
+        <v>45891</v>
       </c>
       <c r="B36" t="n">
-        <v>6.632862567901611</v>
+        <v>6.510205745697021</v>
       </c>
       <c r="C36" t="n">
-        <v>6.887608995385344</v>
+        <v>6.651731906212745</v>
       </c>
       <c r="D36" t="n">
-        <v>6.613991814806306</v>
+        <v>6.330939968556073</v>
       </c>
       <c r="E36" t="n">
-        <v>6.793258064277323</v>
+        <v>6.378115197929731</v>
       </c>
       <c r="F36" t="n">
-        <v>21292005</v>
+        <v>24534090</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45882</v>
+        <v>45894</v>
       </c>
       <c r="B37" t="n">
-        <v>6.349809646606445</v>
+        <v>6.717778205871582</v>
       </c>
       <c r="C37" t="n">
-        <v>6.651732264613072</v>
+        <v>6.830999423066804</v>
       </c>
       <c r="D37" t="n">
-        <v>6.321504696415059</v>
+        <v>6.538511947871742</v>
       </c>
       <c r="E37" t="n">
-        <v>6.613992173559632</v>
+        <v>6.566816897874467</v>
       </c>
       <c r="F37" t="n">
-        <v>21171150</v>
+        <v>16645755</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45883</v>
+        <v>45895</v>
       </c>
       <c r="B38" t="n">
-        <v>6.302634239196777</v>
+        <v>6.604557037353516</v>
       </c>
       <c r="C38" t="n">
-        <v>6.359244610398034</v>
+        <v>6.830999473412895</v>
       </c>
       <c r="D38" t="n">
-        <v>6.161108074996253</v>
+        <v>6.585687228010881</v>
       </c>
       <c r="E38" t="n">
-        <v>6.293198626202678</v>
+        <v>6.670603023434454</v>
       </c>
       <c r="F38" t="n">
-        <v>19710600</v>
+        <v>16930935</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45884</v>
+        <v>45896</v>
       </c>
       <c r="B39" t="n">
-        <v>6.246023178100586</v>
+        <v>6.774388790130615</v>
       </c>
       <c r="C39" t="n">
-        <v>6.302634019725293</v>
+        <v>6.774388790130615</v>
       </c>
       <c r="D39" t="n">
-        <v>6.151672720182234</v>
+        <v>6.491335521831109</v>
       </c>
       <c r="E39" t="n">
-        <v>6.28376421157847</v>
+        <v>6.576251785757814</v>
       </c>
       <c r="F39" t="n">
-        <v>13254045</v>
+        <v>18623850</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45887</v>
+        <v>45897</v>
       </c>
       <c r="B40" t="n">
-        <v>6.519641399383545</v>
+        <v>7.397103786468506</v>
       </c>
       <c r="C40" t="n">
-        <v>6.595121577897451</v>
+        <v>7.519760139399016</v>
       </c>
       <c r="D40" t="n">
-        <v>6.246023272198178</v>
+        <v>6.793258107015099</v>
       </c>
       <c r="E40" t="n">
-        <v>6.246023272198178</v>
+        <v>6.793258107015099</v>
       </c>
       <c r="F40" t="n">
-        <v>17826795</v>
+        <v>45803730</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45888</v>
+        <v>45898</v>
       </c>
       <c r="B41" t="n">
-        <v>6.472465991973877</v>
+        <v>7.727332592010498</v>
       </c>
       <c r="C41" t="n">
-        <v>6.547946173923972</v>
+        <v>7.925469131335989</v>
       </c>
       <c r="D41" t="n">
-        <v>6.340375437363824</v>
+        <v>7.24614230149434</v>
       </c>
       <c r="E41" t="n">
-        <v>6.359244774259185</v>
+        <v>7.331059040964744</v>
       </c>
       <c r="F41" t="n">
-        <v>17640105</v>
+        <v>30910530</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45889</v>
+        <v>45901</v>
       </c>
       <c r="B42" t="n">
-        <v>6.302634239196777</v>
+        <v>7.812247753143311</v>
       </c>
       <c r="C42" t="n">
-        <v>6.538511809390667</v>
+        <v>8.368918213676217</v>
       </c>
       <c r="D42" t="n">
-        <v>6.255458536200094</v>
+        <v>7.736766628410907</v>
       </c>
       <c r="E42" t="n">
-        <v>6.538511809390667</v>
+        <v>7.774507663171871</v>
       </c>
       <c r="F42" t="n">
-        <v>20240430</v>
+        <v>30854040</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45890</v>
+        <v>45902</v>
       </c>
       <c r="B43" t="n">
-        <v>6.302634239196777</v>
+        <v>7.689590930938721</v>
       </c>
       <c r="C43" t="n">
-        <v>6.48190143818941</v>
+        <v>7.963209535894117</v>
       </c>
       <c r="D43" t="n">
-        <v>6.246023395600758</v>
+        <v>7.62354636393504</v>
       </c>
       <c r="E43" t="n">
-        <v>6.264894149194194</v>
+        <v>7.727332438121372</v>
       </c>
       <c r="F43" t="n">
-        <v>15171030</v>
+        <v>15819615</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45891</v>
+        <v>45903</v>
       </c>
       <c r="B44" t="n">
-        <v>6.510205745697021</v>
+        <v>7.755636692047119</v>
       </c>
       <c r="C44" t="n">
-        <v>6.651731906212745</v>
+        <v>7.934903413468593</v>
       </c>
       <c r="D44" t="n">
-        <v>6.330939968556073</v>
+        <v>7.632980340192256</v>
       </c>
       <c r="E44" t="n">
-        <v>6.378115197929731</v>
+        <v>7.736766411393332</v>
       </c>
       <c r="F44" t="n">
-        <v>24534090</v>
+        <v>16418640</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45894</v>
+        <v>45904</v>
       </c>
       <c r="B45" t="n">
-        <v>6.717778205871582</v>
+        <v>8.161346435546875</v>
       </c>
       <c r="C45" t="n">
-        <v>6.830999423066804</v>
+        <v>8.199086054834943</v>
       </c>
       <c r="D45" t="n">
-        <v>6.538511947871742</v>
+        <v>7.699026887569755</v>
       </c>
       <c r="E45" t="n">
-        <v>6.566816897874467</v>
+        <v>7.84998819909073</v>
       </c>
       <c r="F45" t="n">
-        <v>16645755</v>
+        <v>26548620</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45895</v>
+        <v>45905</v>
       </c>
       <c r="B46" t="n">
-        <v>6.604557037353516</v>
+        <v>8.746320724487305</v>
       </c>
       <c r="C46" t="n">
-        <v>6.830999473412895</v>
+        <v>8.746320724487305</v>
       </c>
       <c r="D46" t="n">
-        <v>6.585687228010881</v>
+        <v>8.246260651030823</v>
       </c>
       <c r="E46" t="n">
-        <v>6.670603023434454</v>
+        <v>8.378351670317235</v>
       </c>
       <c r="F46" t="n">
-        <v>16930935</v>
+        <v>32295480</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45896</v>
+        <v>45908</v>
       </c>
       <c r="B47" t="n">
-        <v>6.774388790130615</v>
+        <v>8.406658172607422</v>
       </c>
       <c r="C47" t="n">
-        <v>6.774388790130615</v>
+        <v>8.868976773602627</v>
       </c>
       <c r="D47" t="n">
-        <v>6.491335521831109</v>
+        <v>8.331177044810087</v>
       </c>
       <c r="E47" t="n">
-        <v>6.576251785757814</v>
+        <v>8.821801541124074</v>
       </c>
       <c r="F47" t="n">
-        <v>18623850</v>
+        <v>29259930</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45897</v>
+        <v>45909</v>
       </c>
       <c r="B48" t="n">
-        <v>7.397103786468506</v>
+        <v>8.416093826293945</v>
       </c>
       <c r="C48" t="n">
-        <v>7.519760139399016</v>
+        <v>8.604794757112122</v>
       </c>
       <c r="D48" t="n">
-        <v>6.793258107015099</v>
+        <v>8.33117708472037</v>
       </c>
       <c r="E48" t="n">
-        <v>6.793258107015099</v>
+        <v>8.491574009663303</v>
       </c>
       <c r="F48" t="n">
-        <v>45803730</v>
+        <v>19192110</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45898</v>
+        <v>45910</v>
       </c>
       <c r="B49" t="n">
-        <v>7.727332592010498</v>
+        <v>8.727449417114258</v>
       </c>
       <c r="C49" t="n">
-        <v>7.925469131335989</v>
+        <v>8.972762117589397</v>
       </c>
       <c r="D49" t="n">
-        <v>7.24614230149434</v>
+        <v>8.444398045408148</v>
       </c>
       <c r="E49" t="n">
-        <v>7.331059040964744</v>
+        <v>8.491573274025832</v>
       </c>
       <c r="F49" t="n">
-        <v>30910530</v>
+        <v>32090415</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45901</v>
+        <v>45911</v>
       </c>
       <c r="B50" t="n">
-        <v>7.812247753143311</v>
+        <v>9.43508243560791</v>
       </c>
       <c r="C50" t="n">
-        <v>8.368918213676217</v>
+        <v>9.43508243560791</v>
       </c>
       <c r="D50" t="n">
-        <v>7.736766628410907</v>
+        <v>8.774626343886904</v>
       </c>
       <c r="E50" t="n">
-        <v>7.774507663171871</v>
+        <v>8.821801576554925</v>
       </c>
       <c r="F50" t="n">
-        <v>30854040</v>
+        <v>38184930</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45902</v>
+        <v>45912</v>
       </c>
       <c r="B51" t="n">
-        <v>7.689590930938721</v>
+        <v>9.29355525970459</v>
       </c>
       <c r="C51" t="n">
-        <v>7.963209535894117</v>
+        <v>9.538867022380133</v>
       </c>
       <c r="D51" t="n">
-        <v>7.62354636393504</v>
+        <v>9.18976918691472</v>
       </c>
       <c r="E51" t="n">
-        <v>7.727332438121372</v>
+        <v>9.302990872570676</v>
       </c>
       <c r="F51" t="n">
-        <v>15819615</v>
+        <v>20654025</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45903</v>
+        <v>45915</v>
       </c>
       <c r="B52" t="n">
-        <v>7.755636692047119</v>
+        <v>9.982316017150879</v>
       </c>
       <c r="C52" t="n">
-        <v>7.934903413468593</v>
+        <v>10.22762777379561</v>
       </c>
       <c r="D52" t="n">
-        <v>7.632980340192256</v>
+        <v>9.416210437156936</v>
       </c>
       <c r="E52" t="n">
-        <v>7.736766411393332</v>
+        <v>9.45395194290392</v>
       </c>
       <c r="F52" t="n">
-        <v>16418640</v>
+        <v>28773570</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45904</v>
+        <v>45916</v>
       </c>
       <c r="B53" t="n">
-        <v>8.161346435546875</v>
+        <v>10.13327789306641</v>
       </c>
       <c r="C53" t="n">
-        <v>8.199086054834943</v>
+        <v>10.48237573982321</v>
       </c>
       <c r="D53" t="n">
-        <v>7.699026887569755</v>
+        <v>9.765309764756591</v>
       </c>
       <c r="E53" t="n">
-        <v>7.84998819909073</v>
+        <v>10.22762835604191</v>
       </c>
       <c r="F53" t="n">
-        <v>26548620</v>
+        <v>36285480</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45905</v>
+        <v>45917</v>
       </c>
       <c r="B54" t="n">
-        <v>8.746320724487305</v>
+        <v>10.67107772827148</v>
       </c>
       <c r="C54" t="n">
-        <v>8.746320724487305</v>
+        <v>11.44475361174165</v>
       </c>
       <c r="D54" t="n">
-        <v>8.246260651030823</v>
+        <v>10.13327800484191</v>
       </c>
       <c r="E54" t="n">
-        <v>8.378351670317235</v>
+        <v>10.17101856836423</v>
       </c>
       <c r="F54" t="n">
-        <v>32295480</v>
+        <v>52012695</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45908</v>
+        <v>45918</v>
       </c>
       <c r="B55" t="n">
-        <v>8.406658172607422</v>
+        <v>10.59559726715088</v>
       </c>
       <c r="C55" t="n">
-        <v>8.868976773602627</v>
+        <v>10.80316847148145</v>
       </c>
       <c r="D55" t="n">
-        <v>8.331177044810087</v>
+        <v>10.51068052906581</v>
       </c>
       <c r="E55" t="n">
-        <v>8.821801541124074</v>
+        <v>10.66164183439238</v>
       </c>
       <c r="F55" t="n">
-        <v>29259930</v>
+        <v>20073480</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45909</v>
+        <v>45919</v>
       </c>
       <c r="B56" t="n">
-        <v>8.416093826293945</v>
+        <v>10.4823751449585</v>
       </c>
       <c r="C56" t="n">
-        <v>8.604794757112122</v>
+        <v>10.69938289810835</v>
       </c>
       <c r="D56" t="n">
-        <v>8.33117708472037</v>
+        <v>10.29367422971609</v>
       </c>
       <c r="E56" t="n">
-        <v>8.491574009663303</v>
+        <v>10.66164139235458</v>
       </c>
       <c r="F56" t="n">
-        <v>19192110</v>
+        <v>17667300</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45910</v>
+        <v>45922</v>
       </c>
       <c r="B57" t="n">
-        <v>8.727449417114258</v>
+        <v>10.22762775421143</v>
       </c>
       <c r="C57" t="n">
-        <v>8.972762117589397</v>
+        <v>10.51068007127165</v>
       </c>
       <c r="D57" t="n">
-        <v>8.444398045408148</v>
+        <v>10.1427129094039</v>
       </c>
       <c r="E57" t="n">
-        <v>8.491573274025832</v>
+        <v>10.30310887598188</v>
       </c>
       <c r="F57" t="n">
-        <v>32090415</v>
+        <v>15566775</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45911</v>
+        <v>45923</v>
       </c>
       <c r="B58" t="n">
-        <v>9.43508243560791</v>
+        <v>10.37858963012695</v>
       </c>
       <c r="C58" t="n">
-        <v>9.43508243560791</v>
+        <v>10.7654280387393</v>
       </c>
       <c r="D58" t="n">
-        <v>8.774626343886904</v>
+        <v>10.14271347345069</v>
       </c>
       <c r="E58" t="n">
-        <v>8.821801576554925</v>
+        <v>10.38802524326773</v>
       </c>
       <c r="F58" t="n">
-        <v>38184930</v>
+        <v>26995920</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45912</v>
+        <v>45924</v>
       </c>
       <c r="B59" t="n">
-        <v>9.29355525970459</v>
+        <v>10.26536846160889</v>
       </c>
       <c r="C59" t="n">
-        <v>9.538867022380133</v>
+        <v>10.68051274769255</v>
       </c>
       <c r="D59" t="n">
-        <v>9.18976918691472</v>
+        <v>10.26536846160889</v>
       </c>
       <c r="E59" t="n">
-        <v>9.302990872570676</v>
+        <v>10.42576537526562</v>
       </c>
       <c r="F59" t="n">
-        <v>20654025</v>
+        <v>21153720</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45915</v>
+        <v>45925</v>
       </c>
       <c r="B60" t="n">
-        <v>9.982316017150879</v>
+        <v>10.3974609375</v>
       </c>
       <c r="C60" t="n">
-        <v>10.22762777379561</v>
+        <v>10.97300027594208</v>
       </c>
       <c r="D60" t="n">
-        <v>9.416210437156936</v>
+        <v>10.18045317104418</v>
       </c>
       <c r="E60" t="n">
-        <v>9.45395194290392</v>
+        <v>10.26536896602573</v>
       </c>
       <c r="F60" t="n">
-        <v>28773570</v>
+        <v>37707600</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45916</v>
+        <v>45926</v>
       </c>
       <c r="B61" t="n">
-        <v>10.13327789306641</v>
+        <v>10.5578556060791</v>
       </c>
       <c r="C61" t="n">
-        <v>10.48237573982321</v>
+        <v>10.78429803316605</v>
       </c>
       <c r="D61" t="n">
-        <v>9.765309764756591</v>
+        <v>10.3974605796404</v>
       </c>
       <c r="E61" t="n">
-        <v>10.22762835604191</v>
+        <v>10.5295506569893</v>
       </c>
       <c r="F61" t="n">
-        <v>36285480</v>
+        <v>24341625</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45917</v>
+        <v>45929</v>
       </c>
       <c r="B62" t="n">
-        <v>10.67107772827148</v>
+        <v>10.02005672454834</v>
       </c>
       <c r="C62" t="n">
-        <v>11.44475361174165</v>
+        <v>11.3220975935054</v>
       </c>
       <c r="D62" t="n">
-        <v>10.13327800484191</v>
+        <v>10.02005672454834</v>
       </c>
       <c r="E62" t="n">
-        <v>10.17101856836423</v>
+        <v>10.92582453202877</v>
       </c>
       <c r="F62" t="n">
-        <v>52012695</v>
+        <v>42088620</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45918</v>
+        <v>45930</v>
       </c>
       <c r="B63" t="n">
-        <v>10.59559726715088</v>
+        <v>9.05767822265625</v>
       </c>
       <c r="C63" t="n">
-        <v>10.80316847148145</v>
+        <v>10.33141416366794</v>
       </c>
       <c r="D63" t="n">
-        <v>10.51068052906581</v>
+        <v>9.019937660531136</v>
       </c>
       <c r="E63" t="n">
-        <v>10.66164183439238</v>
+        <v>10.25593303941771</v>
       </c>
       <c r="F63" t="n">
-        <v>20073480</v>
+        <v>53095350</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45919</v>
+        <v>45931</v>
       </c>
       <c r="B64" t="n">
-        <v>10.4823751449585</v>
+        <v>9.05767822265625</v>
       </c>
       <c r="C64" t="n">
-        <v>10.69938289810835</v>
+        <v>9.123723733980441</v>
       </c>
       <c r="D64" t="n">
-        <v>10.29367422971609</v>
+        <v>8.633099260722513</v>
       </c>
       <c r="E64" t="n">
-        <v>10.66164139235458</v>
+        <v>9.114289065843922</v>
       </c>
       <c r="F64" t="n">
-        <v>17667300</v>
+        <v>46123455</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45922</v>
+        <v>45932</v>
       </c>
       <c r="B65" t="n">
-        <v>10.22762775421143</v>
+        <v>8.642535209655762</v>
       </c>
       <c r="C65" t="n">
-        <v>10.51068007127165</v>
+        <v>9.189769602587392</v>
       </c>
       <c r="D65" t="n">
-        <v>10.1427129094039</v>
+        <v>8.585924364267155</v>
       </c>
       <c r="E65" t="n">
-        <v>10.30310887598188</v>
+        <v>9.104854751688817</v>
       </c>
       <c r="F65" t="n">
-        <v>15566775</v>
+        <v>22836450</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45923</v>
+        <v>45933</v>
       </c>
       <c r="B66" t="n">
-        <v>10.37858963012695</v>
+        <v>8.633099555969238</v>
       </c>
       <c r="C66" t="n">
-        <v>10.7654280387393</v>
+        <v>8.80293114655087</v>
       </c>
       <c r="D66" t="n">
-        <v>10.14271347345069</v>
+        <v>8.368918446427164</v>
       </c>
       <c r="E66" t="n">
-        <v>10.38802524326773</v>
+        <v>8.585924324094242</v>
       </c>
       <c r="F66" t="n">
-        <v>26995920</v>
+        <v>34357575</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45924</v>
+        <v>45936</v>
       </c>
       <c r="B67" t="n">
-        <v>10.26536846160889</v>
+        <v>8.453832626342773</v>
       </c>
       <c r="C67" t="n">
-        <v>10.68051274769255</v>
+        <v>8.699145324297035</v>
       </c>
       <c r="D67" t="n">
-        <v>10.26536846160889</v>
+        <v>8.3500465575767</v>
       </c>
       <c r="E67" t="n">
-        <v>10.42576537526562</v>
+        <v>8.633098871163599</v>
       </c>
       <c r="F67" t="n">
-        <v>21153720</v>
+        <v>21915600</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45925</v>
+        <v>45937</v>
       </c>
       <c r="B68" t="n">
-        <v>10.3974609375</v>
+        <v>8.472702026367188</v>
       </c>
       <c r="C68" t="n">
-        <v>10.97300027594208</v>
+        <v>8.472702026367188</v>
       </c>
       <c r="D68" t="n">
-        <v>10.18045317104418</v>
+        <v>8.180215042839338</v>
       </c>
       <c r="E68" t="n">
-        <v>10.26536896602573</v>
+        <v>8.312307005323913</v>
       </c>
       <c r="F68" t="n">
-        <v>37707600</v>
+        <v>21778680</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45926</v>
+        <v>45938</v>
       </c>
       <c r="B69" t="n">
-        <v>10.5578556060791</v>
+        <v>8.576488494873047</v>
       </c>
       <c r="C69" t="n">
-        <v>10.78429803316605</v>
+        <v>8.661405232815047</v>
       </c>
       <c r="D69" t="n">
-        <v>10.3974605796404</v>
+        <v>8.293436165961314</v>
       </c>
       <c r="E69" t="n">
-        <v>10.5295506569893</v>
+        <v>8.585924107884169</v>
       </c>
       <c r="F69" t="n">
-        <v>24341625</v>
+        <v>28115955</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45929</v>
+        <v>45939</v>
       </c>
       <c r="B70" t="n">
-        <v>10.02005672454834</v>
+        <v>8.463268280029297</v>
       </c>
       <c r="C70" t="n">
-        <v>11.3220975935054</v>
+        <v>8.661404806025406</v>
       </c>
       <c r="D70" t="n">
-        <v>10.02005672454834</v>
+        <v>8.35948221075815</v>
       </c>
       <c r="E70" t="n">
-        <v>10.92582453202877</v>
+        <v>8.604793965116739</v>
       </c>
       <c r="F70" t="n">
-        <v>42088620</v>
+        <v>19640250</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45930</v>
+        <v>45940</v>
       </c>
       <c r="B71" t="n">
-        <v>9.05767822265625</v>
+        <v>8.312307357788086</v>
       </c>
       <c r="C71" t="n">
-        <v>10.33141416366794</v>
+        <v>8.633099303056044</v>
       </c>
       <c r="D71" t="n">
-        <v>9.019937660531136</v>
+        <v>8.208521283829853</v>
       </c>
       <c r="E71" t="n">
-        <v>10.25593303941771</v>
+        <v>8.538748842070119</v>
       </c>
       <c r="F71" t="n">
-        <v>53095350</v>
+        <v>20879565</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45931</v>
+        <v>45943</v>
       </c>
       <c r="B72" t="n">
-        <v>9.05767822265625</v>
+        <v>8.114171028137207</v>
       </c>
       <c r="C72" t="n">
-        <v>9.123723733980441</v>
+        <v>8.548183726526958</v>
       </c>
       <c r="D72" t="n">
-        <v>8.633099260722513</v>
+        <v>8.114171028137207</v>
       </c>
       <c r="E72" t="n">
-        <v>9.114289065843922</v>
+        <v>8.491573826418946</v>
       </c>
       <c r="F72" t="n">
-        <v>46123455</v>
+        <v>19664505</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45932</v>
+        <v>45944</v>
       </c>
       <c r="B73" t="n">
-        <v>8.642535209655762</v>
+        <v>8.284001350402832</v>
       </c>
       <c r="C73" t="n">
-        <v>9.189769602587392</v>
+        <v>8.302871631299929</v>
       </c>
       <c r="D73" t="n">
-        <v>8.585924364267155</v>
+        <v>7.982078745628288</v>
       </c>
       <c r="E73" t="n">
-        <v>9.104854751688817</v>
+        <v>8.048124256373375</v>
       </c>
       <c r="F73" t="n">
-        <v>22836450</v>
+        <v>14808465</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>45933</v>
+        <v>45945</v>
       </c>
       <c r="B74" t="n">
-        <v>8.633099555969238</v>
+        <v>8.406658172607422</v>
       </c>
       <c r="C74" t="n">
-        <v>8.80293114655087</v>
+        <v>8.604794715891082</v>
       </c>
       <c r="D74" t="n">
-        <v>8.368918446427164</v>
+        <v>8.227390966483533</v>
       </c>
       <c r="E74" t="n">
-        <v>8.585924324094242</v>
+        <v>8.246261248432866</v>
       </c>
       <c r="F74" t="n">
-        <v>34357575</v>
+        <v>23188515</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45936</v>
+        <v>45946</v>
       </c>
       <c r="B75" t="n">
-        <v>8.453832626342773</v>
+        <v>7.736766815185547</v>
       </c>
       <c r="C75" t="n">
-        <v>8.699145324297035</v>
+        <v>8.35948280249764</v>
       </c>
       <c r="D75" t="n">
-        <v>8.3500465575767</v>
+        <v>7.651851020206387</v>
       </c>
       <c r="E75" t="n">
-        <v>8.633098871163599</v>
+        <v>8.35948280249764</v>
       </c>
       <c r="F75" t="n">
-        <v>21915600</v>
+        <v>40883535</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45937</v>
+        <v>45947</v>
       </c>
       <c r="B76" t="n">
-        <v>8.472702026367188</v>
+        <v>7.925468921661377</v>
       </c>
       <c r="C76" t="n">
-        <v>8.472702026367188</v>
+        <v>7.972644151949453</v>
       </c>
       <c r="D76" t="n">
-        <v>8.180215042839338</v>
+        <v>7.519760240562789</v>
       </c>
       <c r="E76" t="n">
-        <v>8.312307005323913</v>
+        <v>7.632980509817315</v>
       </c>
       <c r="F76" t="n">
-        <v>21778680</v>
+        <v>28614600</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45938</v>
+        <v>45950</v>
       </c>
       <c r="B77" t="n">
-        <v>8.576488494873047</v>
+        <v>7.868857860565186</v>
       </c>
       <c r="C77" t="n">
-        <v>8.661405232815047</v>
+        <v>8.07642905704329</v>
       </c>
       <c r="D77" t="n">
-        <v>8.293436165961314</v>
+        <v>7.868857860565186</v>
       </c>
       <c r="E77" t="n">
-        <v>8.585924107884169</v>
+        <v>8.029253828061425</v>
       </c>
       <c r="F77" t="n">
-        <v>28115955</v>
+        <v>12841500</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45939</v>
+        <v>45951</v>
       </c>
       <c r="B78" t="n">
-        <v>8.463268280029297</v>
+        <v>7.887727737426758</v>
       </c>
       <c r="C78" t="n">
-        <v>8.661404806025406</v>
+        <v>8.038689510752114</v>
       </c>
       <c r="D78" t="n">
-        <v>8.35948221075815</v>
+        <v>7.802812418998699</v>
       </c>
       <c r="E78" t="n">
-        <v>8.604793965116739</v>
+        <v>7.840552508033975</v>
       </c>
       <c r="F78" t="n">
-        <v>19640250</v>
+        <v>13804140</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45940</v>
+        <v>45952</v>
       </c>
       <c r="B79" t="n">
-        <v>8.312307357788086</v>
+        <v>7.868857860565186</v>
       </c>
       <c r="C79" t="n">
-        <v>8.633099303056044</v>
+        <v>7.963209263318409</v>
       </c>
       <c r="D79" t="n">
-        <v>8.208521283829853</v>
+        <v>7.812247491307998</v>
       </c>
       <c r="E79" t="n">
-        <v>8.538748842070119</v>
+        <v>7.963209263318409</v>
       </c>
       <c r="F79" t="n">
-        <v>20879565</v>
+        <v>13535340</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45943</v>
+        <v>45953</v>
       </c>
       <c r="B80" t="n">
-        <v>8.114171028137207</v>
+        <v>7.425409317016602</v>
       </c>
       <c r="C80" t="n">
-        <v>8.548183726526958</v>
+        <v>8.048124341667577</v>
       </c>
       <c r="D80" t="n">
-        <v>8.114171028137207</v>
+        <v>7.095180815001887</v>
       </c>
       <c r="E80" t="n">
-        <v>8.491573826418946</v>
+        <v>8.000949111319624</v>
       </c>
       <c r="F80" t="n">
-        <v>19664505</v>
+        <v>50576925</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45944</v>
+        <v>45954</v>
       </c>
       <c r="B81" t="n">
-        <v>8.284001350402832</v>
+        <v>7.623546123504639</v>
       </c>
       <c r="C81" t="n">
-        <v>8.302871631299929</v>
+        <v>7.755636670530435</v>
       </c>
       <c r="D81" t="n">
-        <v>7.982078745628288</v>
+        <v>7.500889299595316</v>
       </c>
       <c r="E81" t="n">
-        <v>8.048124256373375</v>
+        <v>7.585805089907022</v>
       </c>
       <c r="F81" t="n">
-        <v>14808465</v>
+        <v>23449125</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45945</v>
+        <v>45957</v>
       </c>
       <c r="B82" t="n">
-        <v>8.406658172607422</v>
+        <v>8.038689613342285</v>
       </c>
       <c r="C82" t="n">
-        <v>8.604794715891082</v>
+        <v>8.08586484333712</v>
       </c>
       <c r="D82" t="n">
-        <v>8.227390966483533</v>
+        <v>7.783941765228001</v>
       </c>
       <c r="E82" t="n">
-        <v>8.246261248432866</v>
+        <v>7.783941765228001</v>
       </c>
       <c r="F82" t="n">
-        <v>23188515</v>
+        <v>22558830</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45946</v>
+        <v>45958</v>
       </c>
       <c r="B83" t="n">
-        <v>7.736766815185547</v>
+        <v>8.170781135559082</v>
       </c>
       <c r="C83" t="n">
-        <v>8.35948280249764</v>
+        <v>8.227391037103432</v>
       </c>
       <c r="D83" t="n">
-        <v>7.651851020206387</v>
+        <v>7.87829318001818</v>
       </c>
       <c r="E83" t="n">
-        <v>8.35948280249764</v>
+        <v>8.029254492119065</v>
       </c>
       <c r="F83" t="n">
-        <v>40883535</v>
+        <v>11424210</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45947</v>
+        <v>45959</v>
       </c>
       <c r="B84" t="n">
-        <v>7.925468921661377</v>
+        <v>8.048124313354492</v>
       </c>
       <c r="C84" t="n">
-        <v>7.972644151949453</v>
+        <v>8.321741971115371</v>
       </c>
       <c r="D84" t="n">
-        <v>7.519760240562789</v>
+        <v>8.029254032323792</v>
       </c>
       <c r="E84" t="n">
-        <v>7.632980509817315</v>
+        <v>8.180215335779877</v>
       </c>
       <c r="F84" t="n">
-        <v>28614600</v>
+        <v>13356210</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45950</v>
+        <v>45960</v>
       </c>
       <c r="B85" t="n">
-        <v>7.868857860565186</v>
+        <v>8.019819259643555</v>
       </c>
       <c r="C85" t="n">
-        <v>8.07642905704329</v>
+        <v>8.151910280346781</v>
       </c>
       <c r="D85" t="n">
-        <v>7.868857860565186</v>
+        <v>7.783941694624609</v>
       </c>
       <c r="E85" t="n">
-        <v>8.029253828061425</v>
+        <v>7.859422817763313</v>
       </c>
       <c r="F85" t="n">
-        <v>12841500</v>
+        <v>15100050</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45951</v>
+        <v>45961</v>
       </c>
       <c r="B86" t="n">
-        <v>7.887727737426758</v>
+        <v>7.991513252258301</v>
       </c>
       <c r="C86" t="n">
-        <v>8.038689510752114</v>
+        <v>8.114170548006587</v>
       </c>
       <c r="D86" t="n">
-        <v>7.802812418998699</v>
+        <v>7.812247476935955</v>
       </c>
       <c r="E86" t="n">
-        <v>7.840552508033975</v>
+        <v>8.095299322701166</v>
       </c>
       <c r="F86" t="n">
-        <v>13804140</v>
+        <v>14380065</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45952</v>
+        <v>45964</v>
       </c>
       <c r="B87" t="n">
         <v>7.868857860565186</v>
       </c>
       <c r="C87" t="n">
-        <v>7.963209263318409</v>
+        <v>8.114170562934072</v>
       </c>
       <c r="D87" t="n">
-        <v>7.812247491307998</v>
+        <v>7.821682631583321</v>
       </c>
       <c r="E87" t="n">
-        <v>7.963209263318409</v>
+        <v>8.010384492300274</v>
       </c>
       <c r="F87" t="n">
-        <v>13535340</v>
+        <v>11489310</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45953</v>
+        <v>45965</v>
       </c>
       <c r="B88" t="n">
-        <v>7.425409317016602</v>
+        <v>7.906598091125488</v>
       </c>
       <c r="C88" t="n">
-        <v>8.048124341667577</v>
+        <v>7.925468844409443</v>
       </c>
       <c r="D88" t="n">
-        <v>7.095180815001887</v>
+        <v>7.736766507912199</v>
       </c>
       <c r="E88" t="n">
-        <v>8.000949111319624</v>
+        <v>7.783941737740443</v>
       </c>
       <c r="F88" t="n">
-        <v>50576925</v>
+        <v>7011585</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45954</v>
+        <v>45966</v>
       </c>
       <c r="B89" t="n">
-        <v>7.623546123504639</v>
+        <v>8.246260643005371</v>
       </c>
       <c r="C89" t="n">
-        <v>7.755636670530435</v>
+        <v>8.246260643005371</v>
       </c>
       <c r="D89" t="n">
-        <v>7.500889299595316</v>
+        <v>7.793376743840075</v>
       </c>
       <c r="E89" t="n">
-        <v>7.585805089907022</v>
+        <v>7.906597954828773</v>
       </c>
       <c r="F89" t="n">
-        <v>23449125</v>
+        <v>15467235</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45957</v>
+        <v>45967</v>
       </c>
       <c r="B90" t="n">
-        <v>8.038689613342285</v>
+        <v>7.538629531860352</v>
       </c>
       <c r="C90" t="n">
-        <v>8.08586484333712</v>
+        <v>8.161345969189222</v>
       </c>
       <c r="D90" t="n">
-        <v>7.783941765228001</v>
+        <v>7.519760195689337</v>
       </c>
       <c r="E90" t="n">
-        <v>7.783941765228001</v>
+        <v>8.151910356314202</v>
       </c>
       <c r="F90" t="n">
-        <v>22558830</v>
+        <v>21751275</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45958</v>
+        <v>45968</v>
       </c>
       <c r="B91" t="n">
-        <v>8.170781135559082</v>
+        <v>7.680155754089355</v>
       </c>
       <c r="C91" t="n">
-        <v>8.227391037103432</v>
+        <v>7.972644166465978</v>
       </c>
       <c r="D91" t="n">
-        <v>7.87829318001818</v>
+        <v>7.519760254254706</v>
       </c>
       <c r="E91" t="n">
-        <v>8.029254492119065</v>
+        <v>7.576370625182425</v>
       </c>
       <c r="F91" t="n">
-        <v>11424210</v>
+        <v>27718425</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45959</v>
+        <v>45971</v>
       </c>
       <c r="B92" t="n">
-        <v>8.048124313354492</v>
+        <v>7.944338321685791</v>
       </c>
       <c r="C92" t="n">
-        <v>8.321741971115371</v>
+        <v>8.01038477836644</v>
       </c>
       <c r="D92" t="n">
-        <v>8.029254032323792</v>
+        <v>7.623546375237217</v>
       </c>
       <c r="E92" t="n">
-        <v>8.180215335779877</v>
+        <v>7.831117106733323</v>
       </c>
       <c r="F92" t="n">
-        <v>13356210</v>
+        <v>16046625</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45960</v>
+        <v>45972</v>
       </c>
       <c r="B93" t="n">
-        <v>8.019819259643555</v>
+        <v>8.576488494873047</v>
       </c>
       <c r="C93" t="n">
-        <v>8.151910280346781</v>
+        <v>8.699145795280485</v>
       </c>
       <c r="D93" t="n">
-        <v>7.783941694624609</v>
+        <v>8.029254118282299</v>
       </c>
       <c r="E93" t="n">
-        <v>7.859422817763313</v>
+        <v>8.029254118282299</v>
       </c>
       <c r="F93" t="n">
-        <v>15100050</v>
+        <v>29114505</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45961</v>
+        <v>45973</v>
       </c>
       <c r="B94" t="n">
-        <v>7.991513252258301</v>
+        <v>8.633099555969238</v>
       </c>
       <c r="C94" t="n">
-        <v>8.114170548006587</v>
+        <v>8.661405450925878</v>
       </c>
       <c r="D94" t="n">
-        <v>7.812247476935955</v>
+        <v>8.340612551470524</v>
       </c>
       <c r="E94" t="n">
-        <v>8.095299322701166</v>
+        <v>8.538749092219245</v>
       </c>
       <c r="F94" t="n">
-        <v>14380065</v>
+        <v>15031275</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45964</v>
+        <v>45974</v>
       </c>
       <c r="B95" t="n">
-        <v>7.868857860565186</v>
+        <v>8.548183441162109</v>
       </c>
       <c r="C95" t="n">
-        <v>8.114170562934072</v>
+        <v>8.802930817512539</v>
       </c>
       <c r="D95" t="n">
-        <v>7.821682631583321</v>
+        <v>8.434962699936202</v>
       </c>
       <c r="E95" t="n">
-        <v>8.010384492300274</v>
+        <v>8.633099233278919</v>
       </c>
       <c r="F95" t="n">
-        <v>11489310</v>
+        <v>15416205</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45965</v>
+        <v>45975</v>
       </c>
       <c r="B96" t="n">
-        <v>7.906598091125488</v>
+        <v>9.048243522644043</v>
       </c>
       <c r="C96" t="n">
-        <v>7.925468844409443</v>
+        <v>9.180334544827085</v>
       </c>
       <c r="D96" t="n">
-        <v>7.736766507912199</v>
+        <v>8.463268590923635</v>
       </c>
       <c r="E96" t="n">
-        <v>7.783941737740443</v>
+        <v>8.491573540022996</v>
       </c>
       <c r="F96" t="n">
-        <v>7011585</v>
+        <v>25073685</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45966</v>
+        <v>45978</v>
       </c>
       <c r="B97" t="n">
-        <v>8.246260643005371</v>
+        <v>8.614230155944824</v>
       </c>
       <c r="C97" t="n">
-        <v>8.246260643005371</v>
+        <v>9.180334823876729</v>
       </c>
       <c r="D97" t="n">
-        <v>7.793376743840075</v>
+        <v>8.585924261195547</v>
       </c>
       <c r="E97" t="n">
-        <v>7.906597954828773</v>
+        <v>9.133158647557783</v>
       </c>
       <c r="F97" t="n">
-        <v>15467235</v>
+        <v>17720430</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45967</v>
+        <v>45979</v>
       </c>
       <c r="B98" t="n">
-        <v>7.538629531860352</v>
+        <v>8.93502140045166</v>
       </c>
       <c r="C98" t="n">
-        <v>8.161345969189222</v>
+        <v>9.001067853108248</v>
       </c>
       <c r="D98" t="n">
-        <v>7.519760195689337</v>
+        <v>8.368917722154546</v>
       </c>
       <c r="E98" t="n">
-        <v>8.151910356314202</v>
+        <v>8.397221725082565</v>
       </c>
       <c r="F98" t="n">
-        <v>21751275</v>
+        <v>18369015</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45968</v>
+        <v>45980</v>
       </c>
       <c r="B99" t="n">
-        <v>7.680155754089355</v>
+        <v>8.80293083190918</v>
       </c>
       <c r="C99" t="n">
-        <v>7.972644166465978</v>
+        <v>9.029373259520845</v>
       </c>
       <c r="D99" t="n">
-        <v>7.519760254254706</v>
+        <v>8.80293083190918</v>
       </c>
       <c r="E99" t="n">
-        <v>7.576370625182425</v>
+        <v>8.906716905198296</v>
       </c>
       <c r="F99" t="n">
-        <v>27718425</v>
+        <v>16938915</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45971</v>
+        <v>45982</v>
       </c>
       <c r="B100" t="n">
-        <v>7.944338321685791</v>
+        <v>9.085983276367188</v>
       </c>
       <c r="C100" t="n">
-        <v>8.01038477836644</v>
+        <v>9.09541888940176</v>
       </c>
       <c r="D100" t="n">
-        <v>7.623546375237217</v>
+        <v>8.680274590829329</v>
       </c>
       <c r="E100" t="n">
-        <v>7.831117106733323</v>
+        <v>8.755755715947782</v>
       </c>
       <c r="F100" t="n">
-        <v>16046625</v>
+        <v>25141725</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45972</v>
+        <v>45985</v>
       </c>
       <c r="B101" t="n">
-        <v>8.576488494873047</v>
+        <v>9.340730667114258</v>
       </c>
       <c r="C101" t="n">
-        <v>8.699145795280485</v>
+        <v>9.604913660540712</v>
       </c>
       <c r="D101" t="n">
-        <v>8.029254118282299</v>
+        <v>8.991632825016962</v>
       </c>
       <c r="E101" t="n">
-        <v>8.029254118282299</v>
+        <v>9.010503106318104</v>
       </c>
       <c r="F101" t="n">
-        <v>29114505</v>
+        <v>27962445</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45973</v>
+        <v>45986</v>
       </c>
       <c r="B102" t="n">
-        <v>8.633099555969238</v>
+        <v>9.680394172668457</v>
       </c>
       <c r="C102" t="n">
-        <v>8.661405450925878</v>
+        <v>9.680394172668457</v>
       </c>
       <c r="D102" t="n">
-        <v>8.340612551470524</v>
+        <v>9.199205289764066</v>
       </c>
       <c r="E102" t="n">
-        <v>8.538749092219245</v>
+        <v>9.397341833031193</v>
       </c>
       <c r="F102" t="n">
-        <v>15031275</v>
+        <v>19989270</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45974</v>
+        <v>45987</v>
       </c>
       <c r="B103" t="n">
-        <v>8.548183441162109</v>
+        <v>9.538866996765137</v>
       </c>
       <c r="C103" t="n">
-        <v>8.802930817512539</v>
+        <v>9.765309422679461</v>
       </c>
       <c r="D103" t="n">
-        <v>8.434962699936202</v>
+        <v>9.406776920100254</v>
       </c>
       <c r="E103" t="n">
-        <v>8.633099233278919</v>
+        <v>9.62378278838432</v>
       </c>
       <c r="F103" t="n">
-        <v>15416205</v>
+        <v>18614715</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45975</v>
+        <v>45988</v>
       </c>
       <c r="B104" t="n">
-        <v>9.048243522644043</v>
+        <v>9.54830265045166</v>
       </c>
       <c r="C104" t="n">
-        <v>9.180334544827085</v>
+        <v>9.680393672471112</v>
       </c>
       <c r="D104" t="n">
-        <v>8.463268590923635</v>
+        <v>9.491691807533531</v>
       </c>
       <c r="E104" t="n">
-        <v>8.491573540022996</v>
+        <v>9.595477880488676</v>
       </c>
       <c r="F104" t="n">
-        <v>25073685</v>
+        <v>9577260</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45978</v>
+        <v>45989</v>
       </c>
       <c r="B105" t="n">
-        <v>8.614230155944824</v>
+        <v>9.699263572692871</v>
       </c>
       <c r="C105" t="n">
-        <v>9.180334823876729</v>
+        <v>9.840790202037715</v>
       </c>
       <c r="D105" t="n">
-        <v>8.585924261195547</v>
+        <v>9.463385542188306</v>
       </c>
       <c r="E105" t="n">
-        <v>9.133158647557783</v>
+        <v>9.623782451765093</v>
       </c>
       <c r="F105" t="n">
-        <v>17720430</v>
+        <v>15099000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45979</v>
+        <v>45992</v>
       </c>
       <c r="B106" t="n">
-        <v>8.93502140045166</v>
+        <v>9.755874633789062</v>
       </c>
       <c r="C106" t="n">
-        <v>9.001067853108248</v>
+        <v>9.803049863039947</v>
       </c>
       <c r="D106" t="n">
-        <v>8.368917722154546</v>
+        <v>9.576607439930406</v>
       </c>
       <c r="E106" t="n">
-        <v>8.397221725082565</v>
+        <v>9.737004353130809</v>
       </c>
       <c r="F106" t="n">
-        <v>18369015</v>
+        <v>10236765</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45980</v>
+        <v>45993</v>
       </c>
       <c r="B107" t="n">
-        <v>8.80293083190918</v>
+        <v>9.991751670837402</v>
       </c>
       <c r="C107" t="n">
-        <v>9.029373259520845</v>
+        <v>9.991751670837402</v>
       </c>
       <c r="D107" t="n">
-        <v>8.80293083190918</v>
+        <v>9.718133075166117</v>
       </c>
       <c r="E107" t="n">
-        <v>8.906716905198296</v>
+        <v>9.821919145830901</v>
       </c>
       <c r="F107" t="n">
-        <v>16938915</v>
+        <v>17682945</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45982</v>
+        <v>45994</v>
       </c>
       <c r="B108" t="n">
-        <v>9.085983276367188</v>
+        <v>10.60503101348877</v>
       </c>
       <c r="C108" t="n">
-        <v>9.09541888940176</v>
+        <v>10.60503101348877</v>
       </c>
       <c r="D108" t="n">
-        <v>8.680274590829329</v>
+        <v>10.01062140392657</v>
       </c>
       <c r="E108" t="n">
-        <v>8.755755715947782</v>
+        <v>10.01062140392657</v>
       </c>
       <c r="F108" t="n">
-        <v>25141725</v>
+        <v>23710785</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45985</v>
+        <v>45995</v>
       </c>
       <c r="B109" t="n">
-        <v>9.340730667114258</v>
+        <v>10.99186992645264</v>
       </c>
       <c r="C109" t="n">
-        <v>9.604913660540712</v>
+        <v>11.27492224520904</v>
       </c>
       <c r="D109" t="n">
-        <v>8.991632825016962</v>
+        <v>10.54842164015709</v>
       </c>
       <c r="E109" t="n">
-        <v>9.010503106318104</v>
+        <v>10.68051265925744</v>
       </c>
       <c r="F109" t="n">
-        <v>27962445</v>
+        <v>57664110</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>45986</v>
+        <v>45996</v>
       </c>
       <c r="B110" t="n">
-        <v>9.680394172668457</v>
+        <v>9.916271209716797</v>
       </c>
       <c r="C110" t="n">
-        <v>9.680394172668457</v>
+        <v>11.14283196933208</v>
       </c>
       <c r="D110" t="n">
-        <v>9.199205289764066</v>
+        <v>9.699264386036285</v>
       </c>
       <c r="E110" t="n">
-        <v>9.397341833031193</v>
+        <v>10.96356476449068</v>
       </c>
       <c r="F110" t="n">
-        <v>19989270</v>
+        <v>41284425</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>45987</v>
+        <v>45999</v>
       </c>
       <c r="B111" t="n">
-        <v>9.538866996765137</v>
+        <v>9.944576263427734</v>
       </c>
       <c r="C111" t="n">
-        <v>9.765309422679461</v>
+        <v>10.35971864905989</v>
       </c>
       <c r="D111" t="n">
-        <v>9.406776920100254</v>
+        <v>9.869094197767339</v>
       </c>
       <c r="E111" t="n">
-        <v>9.62378278838432</v>
+        <v>10.16158212395794</v>
       </c>
       <c r="F111" t="n">
-        <v>18614715</v>
+        <v>26651520</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>45988</v>
+        <v>46000</v>
       </c>
       <c r="B112" t="n">
-        <v>9.54830265045166</v>
+        <v>9.453951835632324</v>
       </c>
       <c r="C112" t="n">
-        <v>9.680393672471112</v>
+        <v>9.812484326291873</v>
       </c>
       <c r="D112" t="n">
-        <v>9.491691807533531</v>
+        <v>9.34073015404454</v>
       </c>
       <c r="E112" t="n">
-        <v>9.595477880488676</v>
+        <v>9.765309098025035</v>
       </c>
       <c r="F112" t="n">
-        <v>9577260</v>
+        <v>28289415</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>45989</v>
+        <v>46001</v>
       </c>
       <c r="B113" t="n">
-        <v>9.699263572692871</v>
+        <v>9.425646781921387</v>
       </c>
       <c r="C113" t="n">
-        <v>9.840790202037715</v>
+        <v>9.586043706054708</v>
       </c>
       <c r="D113" t="n">
-        <v>9.463385542188306</v>
+        <v>9.331296316988537</v>
       </c>
       <c r="E113" t="n">
-        <v>9.623782451765093</v>
+        <v>9.548303142165743</v>
       </c>
       <c r="F113" t="n">
-        <v>15099000</v>
+        <v>18250260</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>45992</v>
+        <v>46002</v>
       </c>
       <c r="B114" t="n">
-        <v>9.755874633789062</v>
+        <v>9.03880786895752</v>
       </c>
       <c r="C114" t="n">
-        <v>9.803049863039947</v>
+        <v>9.670958027920365</v>
       </c>
       <c r="D114" t="n">
-        <v>9.576607439930406</v>
+        <v>9.019937588046604</v>
       </c>
       <c r="E114" t="n">
-        <v>9.737004353130809</v>
+        <v>9.350166086803346</v>
       </c>
       <c r="F114" t="n">
-        <v>10236765</v>
+        <v>25851525</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="B115" t="n">
-        <v>9.991751670837402</v>
+        <v>9.31242561340332</v>
       </c>
       <c r="C115" t="n">
-        <v>9.991751670837402</v>
+        <v>9.435081968094138</v>
       </c>
       <c r="D115" t="n">
-        <v>9.718133075166117</v>
+        <v>9.057678235871402</v>
       </c>
       <c r="E115" t="n">
-        <v>9.821919145830901</v>
+        <v>9.133158415442237</v>
       </c>
       <c r="F115" t="n">
-        <v>17682945</v>
+        <v>19101705</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>45994</v>
+        <v>46006</v>
       </c>
       <c r="B116" t="n">
-        <v>10.60503101348877</v>
+        <v>9.284119606018066</v>
       </c>
       <c r="C116" t="n">
-        <v>10.60503101348877</v>
+        <v>9.586043154983601</v>
       </c>
       <c r="D116" t="n">
-        <v>10.01062140392657</v>
+        <v>9.274684937982975</v>
       </c>
       <c r="E116" t="n">
-        <v>10.01062140392657</v>
+        <v>9.48225708265006</v>
       </c>
       <c r="F116" t="n">
-        <v>23710785</v>
+        <v>18610200</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="B117" t="n">
-        <v>10.99186992645264</v>
+        <v>8.963327407836914</v>
       </c>
       <c r="C117" t="n">
-        <v>11.27492224520904</v>
+        <v>9.265249058535124</v>
       </c>
       <c r="D117" t="n">
-        <v>10.54842164015709</v>
+        <v>8.859541338489992</v>
       </c>
       <c r="E117" t="n">
-        <v>10.68051265925744</v>
+        <v>9.161463933977684</v>
       </c>
       <c r="F117" t="n">
-        <v>57664110</v>
+        <v>15605520</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>45996</v>
+        <v>46008</v>
       </c>
       <c r="B118" t="n">
-        <v>9.916271209716797</v>
+        <v>8.680274963378906</v>
       </c>
       <c r="C118" t="n">
-        <v>11.14283196933208</v>
+        <v>8.868976839484423</v>
       </c>
       <c r="D118" t="n">
-        <v>9.699264386036285</v>
+        <v>8.567055160420995</v>
       </c>
       <c r="E118" t="n">
-        <v>10.96356476449068</v>
+        <v>8.868976839484423</v>
       </c>
       <c r="F118" t="n">
-        <v>41284425</v>
+        <v>15643110</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>45999</v>
+        <v>46009</v>
       </c>
       <c r="B119" t="n">
-        <v>9.944576263427734</v>
+        <v>8.82180118560791</v>
       </c>
       <c r="C119" t="n">
-        <v>10.35971864905989</v>
+        <v>8.850107079785973</v>
       </c>
       <c r="D119" t="n">
-        <v>9.869094197767339</v>
+        <v>8.623663705519574</v>
       </c>
       <c r="E119" t="n">
-        <v>10.16158212395794</v>
+        <v>8.642534931497964</v>
       </c>
       <c r="F119" t="n">
-        <v>26651520</v>
+        <v>15603315</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46000</v>
+        <v>46010</v>
       </c>
       <c r="B120" t="n">
-        <v>9.453951835632324</v>
+        <v>8.727449417114258</v>
       </c>
       <c r="C120" t="n">
-        <v>9.812484326291873</v>
+        <v>8.916152221163969</v>
       </c>
       <c r="D120" t="n">
-        <v>9.34073015404454</v>
+        <v>8.708580081498772</v>
       </c>
       <c r="E120" t="n">
-        <v>9.765309098025035</v>
+        <v>8.7934958709264</v>
       </c>
       <c r="F120" t="n">
-        <v>28289415</v>
+        <v>14208075</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46001</v>
+        <v>46013</v>
       </c>
       <c r="B121" t="n">
-        <v>9.425646781921387</v>
+        <v>8.482137680053711</v>
       </c>
       <c r="C121" t="n">
-        <v>9.586043706054708</v>
+        <v>8.774625609788782</v>
       </c>
       <c r="D121" t="n">
-        <v>9.331296316988537</v>
+        <v>8.453832731778846</v>
       </c>
       <c r="E121" t="n">
-        <v>9.548303142165743</v>
+        <v>8.746320661513916</v>
       </c>
       <c r="F121" t="n">
-        <v>18250260</v>
+        <v>15214500</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="B122" t="n">
-        <v>9.03880786895752</v>
+        <v>8.765191078186035</v>
       </c>
       <c r="C122" t="n">
-        <v>9.670958027920365</v>
+        <v>8.850106869119854</v>
       </c>
       <c r="D122" t="n">
-        <v>9.019937588046604</v>
+        <v>8.585923883553804</v>
       </c>
       <c r="E122" t="n">
-        <v>9.350166086803346</v>
+        <v>8.595359496318396</v>
       </c>
       <c r="F122" t="n">
-        <v>25851525</v>
+        <v>14595210</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46003</v>
+        <v>46017</v>
       </c>
       <c r="B123" t="n">
-        <v>9.31242561340332</v>
+        <v>8.727449417114258</v>
       </c>
       <c r="C123" t="n">
-        <v>9.435081968094138</v>
+        <v>8.746320642308715</v>
       </c>
       <c r="D123" t="n">
-        <v>9.057678235871402</v>
+        <v>8.623663347281658</v>
       </c>
       <c r="E123" t="n">
-        <v>9.133158415442237</v>
+        <v>8.69914541369103</v>
       </c>
       <c r="F123" t="n">
-        <v>19101705</v>
+        <v>7410690</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46006</v>
+        <v>46020</v>
       </c>
       <c r="B124" t="n">
-        <v>9.284119606018066</v>
+        <v>8.82180118560791</v>
       </c>
       <c r="C124" t="n">
-        <v>9.586043154983601</v>
+        <v>8.916152591552244</v>
       </c>
       <c r="D124" t="n">
-        <v>9.274684937982975</v>
+        <v>8.651969599697637</v>
       </c>
       <c r="E124" t="n">
-        <v>9.48225708265006</v>
+        <v>8.765191286830836</v>
       </c>
       <c r="F124" t="n">
-        <v>18610200</v>
+        <v>9609180</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46007</v>
+        <v>46021</v>
       </c>
       <c r="B125" t="n">
-        <v>8.963327407836914</v>
+        <v>8.856711387634277</v>
       </c>
       <c r="C125" t="n">
-        <v>9.265249058535124</v>
+        <v>9.153916670664056</v>
       </c>
       <c r="D125" t="n">
-        <v>8.859541338489992</v>
+        <v>8.787363834683498</v>
       </c>
       <c r="E125" t="n">
-        <v>9.161463933977684</v>
+        <v>9.124196425797942</v>
       </c>
       <c r="F125" t="n">
-        <v>15605520</v>
+        <v>12866200</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46008</v>
+        <v>46024</v>
       </c>
       <c r="B126" t="n">
-        <v>8.680274963378906</v>
+        <v>8.747735977172852</v>
       </c>
       <c r="C126" t="n">
-        <v>8.868976839484423</v>
+        <v>9.03503417893951</v>
       </c>
       <c r="D126" t="n">
-        <v>8.567055160420995</v>
+        <v>8.648667240788697</v>
       </c>
       <c r="E126" t="n">
-        <v>8.868976839484423</v>
+        <v>8.955779567747983</v>
       </c>
       <c r="F126" t="n">
-        <v>15643110</v>
+        <v>11298000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46009</v>
+        <v>46027</v>
       </c>
       <c r="B127" t="n">
-        <v>8.82180118560791</v>
+        <v>8.866618156433105</v>
       </c>
       <c r="C127" t="n">
-        <v>8.850107079785973</v>
+        <v>8.955779832860344</v>
       </c>
       <c r="D127" t="n">
-        <v>8.623663705519574</v>
+        <v>8.609040190040977</v>
       </c>
       <c r="E127" t="n">
-        <v>8.642534931497964</v>
+        <v>8.777456480005867</v>
       </c>
       <c r="F127" t="n">
-        <v>15603315</v>
+        <v>12352300</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46010</v>
+        <v>46028</v>
       </c>
       <c r="B128" t="n">
-        <v>8.727449417114258</v>
+        <v>9.064754486083984</v>
       </c>
       <c r="C128" t="n">
-        <v>8.916152221163969</v>
+        <v>9.302519266130554</v>
       </c>
       <c r="D128" t="n">
-        <v>8.708580081498772</v>
+        <v>8.916152325245688</v>
       </c>
       <c r="E128" t="n">
-        <v>8.7934958709264</v>
+        <v>8.916152325245688</v>
       </c>
       <c r="F128" t="n">
-        <v>14208075</v>
+        <v>14943300</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46013</v>
+        <v>46029</v>
       </c>
       <c r="B129" t="n">
-        <v>8.482137680053711</v>
+        <v>9.203451156616211</v>
       </c>
       <c r="C129" t="n">
-        <v>8.774625609788782</v>
+        <v>9.203451156616211</v>
       </c>
       <c r="D129" t="n">
-        <v>8.453832731778846</v>
+        <v>8.688296145098166</v>
       </c>
       <c r="E129" t="n">
-        <v>8.746320661513916</v>
+        <v>9.054848985644934</v>
       </c>
       <c r="F129" t="n">
-        <v>15214500</v>
+        <v>23440400</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46014</v>
+        <v>46030</v>
       </c>
       <c r="B130" t="n">
-        <v>8.765191078186035</v>
+        <v>9.134102821350098</v>
       </c>
       <c r="C130" t="n">
-        <v>8.850106869119854</v>
+        <v>9.361959589984128</v>
       </c>
       <c r="D130" t="n">
-        <v>8.585923883553804</v>
+        <v>9.134102821350098</v>
       </c>
       <c r="E130" t="n">
-        <v>8.595359496318396</v>
+        <v>9.134102821350098</v>
       </c>
       <c r="F130" t="n">
-        <v>14595210</v>
+        <v>12980200</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46017</v>
+        <v>46031</v>
       </c>
       <c r="B131" t="n">
-        <v>8.727449417114258</v>
+        <v>8.797270774841309</v>
       </c>
       <c r="C131" t="n">
-        <v>8.746320642308715</v>
+        <v>9.223265039384616</v>
       </c>
       <c r="D131" t="n">
-        <v>8.623663347281658</v>
+        <v>8.747736404231</v>
       </c>
       <c r="E131" t="n">
-        <v>8.69914541369103</v>
+        <v>9.163823605694338</v>
       </c>
       <c r="F131" t="n">
-        <v>7410690</v>
+        <v>22469000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46020</v>
+        <v>46034</v>
       </c>
       <c r="B132" t="n">
-        <v>8.82180118560791</v>
+        <v>8.500065803527832</v>
       </c>
       <c r="C132" t="n">
-        <v>8.916152591552244</v>
+        <v>8.866618647643884</v>
       </c>
       <c r="D132" t="n">
-        <v>8.651969599697637</v>
+        <v>8.500065803527832</v>
       </c>
       <c r="E132" t="n">
-        <v>8.765191286830836</v>
+        <v>8.84680546555658</v>
       </c>
       <c r="F132" t="n">
-        <v>9609180</v>
+        <v>13347200</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46021</v>
+        <v>46035</v>
       </c>
       <c r="B133" t="n">
-        <v>8.856711387634277</v>
+        <v>8.123605728149414</v>
       </c>
       <c r="C133" t="n">
-        <v>9.153916670664056</v>
+        <v>8.470345383014937</v>
       </c>
       <c r="D133" t="n">
-        <v>8.787363834683498</v>
+        <v>7.975003558801077</v>
       </c>
       <c r="E133" t="n">
-        <v>9.124196425797942</v>
+        <v>8.470345383014937</v>
       </c>
       <c r="F133" t="n">
-        <v>12866200</v>
+        <v>28401800</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46024</v>
+        <v>46036</v>
       </c>
       <c r="B134" t="n">
-        <v>8.747735977172852</v>
+        <v>8.321742057800293</v>
       </c>
       <c r="C134" t="n">
-        <v>9.03503417893951</v>
+        <v>8.361369364940693</v>
       </c>
       <c r="D134" t="n">
-        <v>8.648667240788697</v>
+        <v>8.103792340922855</v>
       </c>
       <c r="E134" t="n">
-        <v>8.955779567747983</v>
+        <v>8.222674262344055</v>
       </c>
       <c r="F134" t="n">
-        <v>11298000</v>
+        <v>20752400</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46027</v>
+        <v>46037</v>
       </c>
       <c r="B135" t="n">
-        <v>8.866618156433105</v>
+        <v>8.658574104309082</v>
       </c>
       <c r="C135" t="n">
-        <v>8.955779832860344</v>
+        <v>9.015220791260507</v>
       </c>
       <c r="D135" t="n">
-        <v>8.609040190040977</v>
+        <v>8.321741542094722</v>
       </c>
       <c r="E135" t="n">
-        <v>8.777456480005867</v>
+        <v>8.321741542094722</v>
       </c>
       <c r="F135" t="n">
-        <v>12352300</v>
+        <v>28392200</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46028</v>
+        <v>46038</v>
       </c>
       <c r="B136" t="n">
-        <v>9.064754486083984</v>
+        <v>8.381183624267578</v>
       </c>
       <c r="C136" t="n">
-        <v>9.302519266130554</v>
+        <v>8.698202086435199</v>
       </c>
       <c r="D136" t="n">
-        <v>8.916152325245688</v>
+        <v>8.252394637814596</v>
       </c>
       <c r="E136" t="n">
-        <v>8.916152325245688</v>
+        <v>8.698202086435199</v>
       </c>
       <c r="F136" t="n">
-        <v>14943300</v>
+        <v>17107700</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46029</v>
+        <v>46041</v>
       </c>
       <c r="B137" t="n">
-        <v>9.203451156616211</v>
+        <v>8.28211498260498</v>
       </c>
       <c r="C137" t="n">
-        <v>9.203451156616211</v>
+        <v>8.420811033875403</v>
       </c>
       <c r="D137" t="n">
-        <v>8.688296145098166</v>
+        <v>8.222674492624479</v>
       </c>
       <c r="E137" t="n">
-        <v>9.054848985644934</v>
+        <v>8.351463480634969</v>
       </c>
       <c r="F137" t="n">
-        <v>23440400</v>
+        <v>9710200</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46030</v>
+        <v>46042</v>
       </c>
       <c r="B138" t="n">
-        <v>9.134102821350098</v>
+        <v>8.321742057800293</v>
       </c>
       <c r="C138" t="n">
-        <v>9.361959589984128</v>
+        <v>8.747736318151743</v>
       </c>
       <c r="D138" t="n">
-        <v>9.134102821350098</v>
+        <v>8.103792340922855</v>
       </c>
       <c r="E138" t="n">
-        <v>9.134102821350098</v>
+        <v>8.192954018186137</v>
       </c>
       <c r="F138" t="n">
-        <v>12980200</v>
+        <v>22970000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="B139" t="n">
-        <v>8.797270774841309</v>
+        <v>8.727923393249512</v>
       </c>
       <c r="C139" t="n">
-        <v>9.223265039384616</v>
+        <v>8.747736575006712</v>
       </c>
       <c r="D139" t="n">
-        <v>8.747736404231</v>
+        <v>8.430718108575071</v>
       </c>
       <c r="E139" t="n">
-        <v>9.163823605694338</v>
+        <v>8.579320278517514</v>
       </c>
       <c r="F139" t="n">
-        <v>22469000</v>
+        <v>16727100</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46034</v>
+        <v>46044</v>
       </c>
       <c r="B140" t="n">
-        <v>8.500065803527832</v>
+        <v>8.876524925231934</v>
       </c>
       <c r="C140" t="n">
-        <v>8.866618647643884</v>
+        <v>9.193543368879311</v>
       </c>
       <c r="D140" t="n">
-        <v>8.500065803527832</v>
+        <v>8.747735946302814</v>
       </c>
       <c r="E140" t="n">
-        <v>8.84680546555658</v>
+        <v>8.76755007142552</v>
       </c>
       <c r="F140" t="n">
-        <v>13347200</v>
+        <v>24288200</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46035</v>
+        <v>46045</v>
       </c>
       <c r="B141" t="n">
-        <v>8.123605728149414</v>
+        <v>9.282705307006836</v>
       </c>
       <c r="C141" t="n">
-        <v>8.470345383014937</v>
+        <v>9.332239676436359</v>
       </c>
       <c r="D141" t="n">
-        <v>7.975003558801077</v>
+        <v>8.718015951963013</v>
       </c>
       <c r="E141" t="n">
-        <v>8.470345383014937</v>
+        <v>8.935966610579204</v>
       </c>
       <c r="F141" t="n">
-        <v>28401800</v>
+        <v>23389800</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46036</v>
+        <v>46048</v>
       </c>
       <c r="B142" t="n">
-        <v>8.321742057800293</v>
+        <v>9.381773948669434</v>
       </c>
       <c r="C142" t="n">
-        <v>8.361369364940693</v>
+        <v>9.490748804453778</v>
       </c>
       <c r="D142" t="n">
-        <v>8.103792340922855</v>
+        <v>9.15391622957007</v>
       </c>
       <c r="E142" t="n">
-        <v>8.222674262344055</v>
+        <v>9.322332517011924</v>
       </c>
       <c r="F142" t="n">
-        <v>20752400</v>
+        <v>18407500</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46037</v>
+        <v>46049</v>
       </c>
       <c r="B143" t="n">
-        <v>8.658574104309082</v>
+        <v>9.550189971923828</v>
       </c>
       <c r="C143" t="n">
-        <v>9.015220791260507</v>
+        <v>9.80776698254232</v>
       </c>
       <c r="D143" t="n">
-        <v>8.321741542094722</v>
+        <v>9.520468784522501</v>
       </c>
       <c r="E143" t="n">
-        <v>8.321741542094722</v>
+        <v>9.609630457147528</v>
       </c>
       <c r="F143" t="n">
-        <v>28392200</v>
+        <v>16735000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46038</v>
+        <v>46050</v>
       </c>
       <c r="B144" t="n">
-        <v>8.381183624267578</v>
+        <v>9.986090660095215</v>
       </c>
       <c r="C144" t="n">
-        <v>8.698202086435199</v>
+        <v>9.986090660095215</v>
       </c>
       <c r="D144" t="n">
-        <v>8.252394637814596</v>
+        <v>9.589817596119019</v>
       </c>
       <c r="E144" t="n">
-        <v>8.698202086435199</v>
+        <v>9.649258083320694</v>
       </c>
       <c r="F144" t="n">
-        <v>17107700</v>
+        <v>20719000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46041</v>
+        <v>46051</v>
       </c>
       <c r="B145" t="n">
-        <v>8.28211498260498</v>
+        <v>9.62944507598877</v>
       </c>
       <c r="C145" t="n">
-        <v>8.420811033875403</v>
+        <v>10.3427366039957</v>
       </c>
       <c r="D145" t="n">
-        <v>8.222674492624479</v>
+        <v>9.391680288530267</v>
       </c>
       <c r="E145" t="n">
-        <v>8.351463480634969</v>
+        <v>10.23376174563646</v>
       </c>
       <c r="F145" t="n">
-        <v>9710200</v>
+        <v>28116600</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46042</v>
+        <v>46052</v>
       </c>
       <c r="B146" t="n">
-        <v>8.321742057800293</v>
+        <v>9.698792457580566</v>
       </c>
       <c r="C146" t="n">
-        <v>8.747736318151743</v>
+        <v>9.906836052474103</v>
       </c>
       <c r="D146" t="n">
-        <v>8.103792340922855</v>
+        <v>9.490748862687029</v>
       </c>
       <c r="E146" t="n">
-        <v>8.192954018186137</v>
+        <v>9.490748862687029</v>
       </c>
       <c r="F146" t="n">
-        <v>22970000</v>
+        <v>19854300</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46043</v>
+        <v>46055</v>
       </c>
       <c r="B147" t="n">
-        <v>8.727923393249512</v>
+        <v>9.738419532775879</v>
       </c>
       <c r="C147" t="n">
-        <v>8.747736575006712</v>
+        <v>9.787953900820037</v>
       </c>
       <c r="D147" t="n">
-        <v>8.430718108575071</v>
+        <v>9.54028300538873</v>
       </c>
       <c r="E147" t="n">
-        <v>8.579320278517514</v>
+        <v>9.688885164731719</v>
       </c>
       <c r="F147" t="n">
-        <v>16727100</v>
+        <v>14726400</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46044</v>
+        <v>46056</v>
       </c>
       <c r="B148" t="n">
-        <v>8.876524925231934</v>
+        <v>10.02571773529053</v>
       </c>
       <c r="C148" t="n">
-        <v>9.193543368879311</v>
+        <v>10.17432083944681</v>
       </c>
       <c r="D148" t="n">
-        <v>8.747735946302814</v>
+        <v>9.877115575923735</v>
       </c>
       <c r="E148" t="n">
-        <v>8.76755007142552</v>
+        <v>9.976183367238434</v>
       </c>
       <c r="F148" t="n">
-        <v>24288200</v>
+        <v>22715700</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46045</v>
+        <v>46057</v>
       </c>
       <c r="B149" t="n">
-        <v>9.282705307006836</v>
+        <v>9.639350891113281</v>
       </c>
       <c r="C149" t="n">
-        <v>9.332239676436359</v>
+        <v>10.07525220042452</v>
       </c>
       <c r="D149" t="n">
-        <v>8.718015951963013</v>
+        <v>9.570003342045831</v>
       </c>
       <c r="E149" t="n">
-        <v>8.935966610579204</v>
+        <v>9.906835914298293</v>
       </c>
       <c r="F149" t="n">
-        <v>23389800</v>
+        <v>21355600</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46048</v>
+        <v>46058</v>
       </c>
       <c r="B150" t="n">
-        <v>9.381773948669434</v>
+        <v>9.560096740722656</v>
       </c>
       <c r="C150" t="n">
-        <v>9.490748804453778</v>
+        <v>9.847394958309847</v>
       </c>
       <c r="D150" t="n">
-        <v>9.15391622957007</v>
+        <v>9.560096740722656</v>
       </c>
       <c r="E150" t="n">
-        <v>9.322332517011924</v>
+        <v>9.688885727198231</v>
       </c>
       <c r="F150" t="n">
-        <v>18407500</v>
+        <v>13183300</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46049</v>
+        <v>46059</v>
       </c>
       <c r="B151" t="n">
-        <v>9.550189971923828</v>
+        <v>10.10497283935547</v>
       </c>
       <c r="C151" t="n">
-        <v>9.80776698254232</v>
+        <v>10.10497283935547</v>
       </c>
       <c r="D151" t="n">
-        <v>9.520468784522501</v>
+        <v>9.153916516546158</v>
       </c>
       <c r="E151" t="n">
-        <v>9.609630457147528</v>
+        <v>9.56009665377282</v>
       </c>
       <c r="F151" t="n">
-        <v>16735000</v>
+        <v>35563900</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46050</v>
+        <v>46062</v>
       </c>
       <c r="B152" t="n">
-        <v>9.986090660095215</v>
+        <v>10.86779975891113</v>
       </c>
       <c r="C152" t="n">
-        <v>9.986090660095215</v>
+        <v>10.86779975891113</v>
       </c>
       <c r="D152" t="n">
-        <v>9.589817596119019</v>
+        <v>9.956370737583169</v>
       </c>
       <c r="E152" t="n">
-        <v>9.649258083320694</v>
+        <v>10.16441433907737</v>
       </c>
       <c r="F152" t="n">
-        <v>20719000</v>
+        <v>23799100</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46051</v>
+        <v>46063</v>
       </c>
       <c r="B153" t="n">
-        <v>9.62944507598877</v>
+        <v>10.50124645233154</v>
       </c>
       <c r="C153" t="n">
-        <v>10.3427366039957</v>
+        <v>10.92723975440287</v>
       </c>
       <c r="D153" t="n">
-        <v>9.391680288530267</v>
+        <v>10.46161914644608</v>
       </c>
       <c r="E153" t="n">
-        <v>10.23376174563646</v>
+        <v>10.75882346819229</v>
       </c>
       <c r="F153" t="n">
-        <v>28116600</v>
+        <v>15416300</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="B154" t="n">
-        <v>9.698792457580566</v>
+        <v>10.99658870697021</v>
       </c>
       <c r="C154" t="n">
-        <v>9.906836052474103</v>
+        <v>11.05602919588296</v>
       </c>
       <c r="D154" t="n">
-        <v>9.490748862687029</v>
+        <v>10.62012881296118</v>
       </c>
       <c r="E154" t="n">
-        <v>9.490748862687029</v>
+        <v>10.71919660941227</v>
       </c>
       <c r="F154" t="n">
-        <v>19854300</v>
+        <v>16601200</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46055</v>
+        <v>46065</v>
       </c>
       <c r="B155" t="n">
-        <v>9.738419532775879</v>
+        <v>10.05543804168701</v>
       </c>
       <c r="C155" t="n">
-        <v>9.787953900820037</v>
+        <v>11.01640138672213</v>
       </c>
       <c r="D155" t="n">
-        <v>9.54028300538873</v>
+        <v>10.04553192384564</v>
       </c>
       <c r="E155" t="n">
-        <v>9.688885164731719</v>
+        <v>10.90742653215115</v>
       </c>
       <c r="F155" t="n">
-        <v>14726400</v>
+        <v>26023100</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46056</v>
+        <v>46066</v>
       </c>
       <c r="B156" t="n">
-        <v>10.02571773529053</v>
+        <v>10.13469314575195</v>
       </c>
       <c r="C156" t="n">
-        <v>10.17432083944681</v>
+        <v>10.26348213184445</v>
       </c>
       <c r="D156" t="n">
-        <v>9.877115575923735</v>
+        <v>9.678979580056321</v>
       </c>
       <c r="E156" t="n">
-        <v>9.976183367238434</v>
+        <v>9.797861503036426</v>
       </c>
       <c r="F156" t="n">
-        <v>22715700</v>
+        <v>19363800</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46057</v>
+        <v>46071</v>
       </c>
       <c r="B157" t="n">
-        <v>9.639350891113281</v>
+        <v>10.18422698974609</v>
       </c>
       <c r="C157" t="n">
-        <v>10.07525220042452</v>
+        <v>10.32292303177694</v>
       </c>
       <c r="D157" t="n">
-        <v>9.570003342045831</v>
+        <v>10.04553189250473</v>
       </c>
       <c r="E157" t="n">
-        <v>9.906835914298293</v>
+        <v>10.13469262153583</v>
       </c>
       <c r="F157" t="n">
-        <v>21355600</v>
+        <v>10535300</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46058</v>
+        <v>46072</v>
       </c>
       <c r="B158" t="n">
-        <v>9.560096740722656</v>
+        <v>10.48143291473389</v>
       </c>
       <c r="C158" t="n">
-        <v>9.847394958309847</v>
+        <v>10.72910382660338</v>
       </c>
       <c r="D158" t="n">
-        <v>9.560096740722656</v>
+        <v>10.15450738664932</v>
       </c>
       <c r="E158" t="n">
-        <v>9.688885727198231</v>
+        <v>10.19413469475685</v>
       </c>
       <c r="F158" t="n">
-        <v>13183300</v>
+        <v>15969100</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46059</v>
+        <v>46073</v>
       </c>
       <c r="B159" t="n">
-        <v>10.10497283935547</v>
+        <v>10.69938278198242</v>
       </c>
       <c r="C159" t="n">
-        <v>10.10497283935547</v>
+        <v>10.76873032978976</v>
       </c>
       <c r="D159" t="n">
-        <v>9.153916516546158</v>
+        <v>10.28329560555942</v>
       </c>
       <c r="E159" t="n">
-        <v>9.56009665377282</v>
+        <v>10.37245727833428</v>
       </c>
       <c r="F159" t="n">
-        <v>35563900</v>
+        <v>15490100</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46062</v>
+        <v>46076</v>
       </c>
       <c r="B160" t="n">
-        <v>10.86779975891113</v>
+        <v>10.27338886260986</v>
       </c>
       <c r="C160" t="n">
-        <v>10.86779975891113</v>
+        <v>10.76873066473063</v>
       </c>
       <c r="D160" t="n">
-        <v>9.956370737583169</v>
+        <v>10.22385449343989</v>
       </c>
       <c r="E160" t="n">
-        <v>10.16441433907737</v>
+        <v>10.60031437642641</v>
       </c>
       <c r="F160" t="n">
-        <v>23799100</v>
+        <v>17659300</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46063</v>
+        <v>46077</v>
       </c>
       <c r="B161" t="n">
-        <v>10.50124645233154</v>
+        <v>10.03562545776367</v>
       </c>
       <c r="C161" t="n">
-        <v>10.92723975440287</v>
+        <v>10.44180560187863</v>
       </c>
       <c r="D161" t="n">
-        <v>10.46161914644608</v>
+        <v>10.00590521289392</v>
       </c>
       <c r="E161" t="n">
-        <v>10.75882346819229</v>
+        <v>10.35264392247983</v>
       </c>
       <c r="F161" t="n">
-        <v>15416300</v>
+        <v>19247800</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46064</v>
+        <v>46078</v>
       </c>
       <c r="B162" t="n">
-        <v>10.99658870697021</v>
+        <v>9.40158748626709</v>
       </c>
       <c r="C162" t="n">
-        <v>11.05602919588296</v>
+        <v>10.17432140320185</v>
       </c>
       <c r="D162" t="n">
-        <v>10.62012881296118</v>
+        <v>9.32233287090807</v>
       </c>
       <c r="E162" t="n">
-        <v>10.71919660941227</v>
+        <v>10.15450727696733</v>
       </c>
       <c r="F162" t="n">
-        <v>16601200</v>
+        <v>25004500</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46065</v>
+        <v>46079</v>
       </c>
       <c r="B163" t="n">
-        <v>10.05543804168701</v>
+        <v>9.490749359130859</v>
       </c>
       <c r="C163" t="n">
-        <v>11.01640138672213</v>
+        <v>9.599724221284127</v>
       </c>
       <c r="D163" t="n">
-        <v>10.04553192384564</v>
+        <v>9.381774496977592</v>
       </c>
       <c r="E163" t="n">
-        <v>10.90742653215115</v>
+        <v>9.42140180546874</v>
       </c>
       <c r="F163" t="n">
-        <v>26023100</v>
+        <v>12048700</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46066</v>
+        <v>46080</v>
       </c>
       <c r="B164" t="n">
-        <v>10.13469314575195</v>
+        <v>9.26289176940918</v>
       </c>
       <c r="C164" t="n">
-        <v>10.26348213184445</v>
+        <v>9.560096084962412</v>
       </c>
       <c r="D164" t="n">
-        <v>9.678979580056321</v>
+        <v>9.26289176940918</v>
       </c>
       <c r="E164" t="n">
-        <v>9.797861503036426</v>
+        <v>9.391679802261192</v>
       </c>
       <c r="F164" t="n">
-        <v>19363800</v>
+        <v>11244700</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46071</v>
+        <v>46083</v>
       </c>
       <c r="B165" t="n">
-        <v>10.18422698974609</v>
+        <v>9.104381561279297</v>
       </c>
       <c r="C165" t="n">
-        <v>10.32292303177694</v>
+        <v>9.262891725557282</v>
       </c>
       <c r="D165" t="n">
-        <v>10.04553189250473</v>
+        <v>8.807177247133072</v>
       </c>
       <c r="E165" t="n">
-        <v>10.13469262153583</v>
+        <v>8.965686466621586</v>
       </c>
       <c r="F165" t="n">
-        <v>10535300</v>
+        <v>17947600</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46072</v>
+        <v>46084</v>
       </c>
       <c r="B166" t="n">
-        <v>10.48143291473389</v>
+        <v>8.916152954101562</v>
       </c>
       <c r="C166" t="n">
-        <v>10.72910382660338</v>
+        <v>9.084569252151091</v>
       </c>
       <c r="D166" t="n">
-        <v>10.15450738664932</v>
+        <v>8.470345495354398</v>
       </c>
       <c r="E166" t="n">
-        <v>10.19413469475685</v>
+        <v>8.757643719417198</v>
       </c>
       <c r="F166" t="n">
-        <v>15969100</v>
+        <v>23872900</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46073</v>
+        <v>46085</v>
       </c>
       <c r="B167" t="n">
-        <v>10.69938278198242</v>
+        <v>9.441214561462402</v>
       </c>
       <c r="C167" t="n">
-        <v>10.76873032978976</v>
+        <v>9.461028687209016</v>
       </c>
       <c r="D167" t="n">
-        <v>10.28329560555942</v>
+        <v>9.035034431551976</v>
       </c>
       <c r="E167" t="n">
-        <v>10.37245727833428</v>
+        <v>9.163823414536418</v>
       </c>
       <c r="F167" t="n">
-        <v>15490100</v>
+        <v>17524500</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="B168" t="n">
-        <v>10.27338886260986</v>
+        <v>9.074662208557129</v>
       </c>
       <c r="C168" t="n">
-        <v>10.76873066473063</v>
+        <v>9.500656486291655</v>
       </c>
       <c r="D168" t="n">
-        <v>10.22385449343989</v>
+        <v>9.044941963186449</v>
       </c>
       <c r="E168" t="n">
-        <v>10.60031437642641</v>
+        <v>9.371867496632623</v>
       </c>
       <c r="F168" t="n">
-        <v>17659300</v>
+        <v>20521200</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46077</v>
+        <v>46087</v>
       </c>
       <c r="B169" t="n">
-        <v>10.03562545776367</v>
+        <v>9.243078231811523</v>
       </c>
       <c r="C169" t="n">
-        <v>10.44180560187863</v>
+        <v>9.391680399030671</v>
       </c>
       <c r="D169" t="n">
-        <v>10.00590521289392</v>
+        <v>9.015221449436892</v>
       </c>
       <c r="E169" t="n">
-        <v>10.35264392247983</v>
+        <v>9.064754875316916</v>
       </c>
       <c r="F169" t="n">
-        <v>19247800</v>
+        <v>18677300</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="B170" t="n">
-        <v>9.40158748626709</v>
+        <v>9.431308746337891</v>
       </c>
       <c r="C170" t="n">
-        <v>10.17432140320185</v>
+        <v>9.431308746337891</v>
       </c>
       <c r="D170" t="n">
-        <v>9.32233287090807</v>
+        <v>9.064754966566955</v>
       </c>
       <c r="E170" t="n">
-        <v>10.15450727696733</v>
+        <v>9.134103464118251</v>
       </c>
       <c r="F170" t="n">
-        <v>25004500</v>
+        <v>16425800</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46079</v>
+        <v>46091</v>
       </c>
       <c r="B171" t="n">
-        <v>9.490749359130859</v>
+        <v>10.0455322265625</v>
       </c>
       <c r="C171" t="n">
-        <v>9.599724221284127</v>
+        <v>10.25357582413239</v>
       </c>
       <c r="D171" t="n">
-        <v>9.381774496977592</v>
+        <v>9.510563110638433</v>
       </c>
       <c r="E171" t="n">
-        <v>9.42140180546874</v>
+        <v>9.55019041756653</v>
       </c>
       <c r="F171" t="n">
-        <v>12048700</v>
+        <v>21417000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46080</v>
+        <v>46092</v>
       </c>
       <c r="B172" t="n">
-        <v>9.26289176940918</v>
+        <v>9.946463584899902</v>
       </c>
       <c r="C172" t="n">
-        <v>9.560096084962412</v>
+        <v>10.21394861789357</v>
       </c>
       <c r="D172" t="n">
-        <v>9.26289176940918</v>
+        <v>9.867208970262416</v>
       </c>
       <c r="E172" t="n">
-        <v>9.391679802261192</v>
+        <v>9.90683627758116</v>
       </c>
       <c r="F172" t="n">
-        <v>11244700</v>
+        <v>13112300</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46083</v>
+        <v>46093</v>
       </c>
       <c r="B173" t="n">
-        <v>9.104381561279297</v>
+        <v>9.31242561340332</v>
       </c>
       <c r="C173" t="n">
-        <v>9.262891725557282</v>
+        <v>9.896929098067334</v>
       </c>
       <c r="D173" t="n">
-        <v>8.807177247133072</v>
+        <v>9.243078062609122</v>
       </c>
       <c r="E173" t="n">
-        <v>8.965686466621586</v>
+        <v>9.817674484362673</v>
       </c>
       <c r="F173" t="n">
-        <v>17947600</v>
+        <v>14948600</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46084</v>
+        <v>46094</v>
       </c>
       <c r="B174" t="n">
-        <v>8.916152954101562</v>
+        <v>9.252985000610352</v>
       </c>
       <c r="C174" t="n">
-        <v>9.084569252151091</v>
+        <v>10.23376154055783</v>
       </c>
       <c r="D174" t="n">
-        <v>8.470345495354398</v>
+        <v>9.064754587010629</v>
       </c>
       <c r="E174" t="n">
-        <v>8.757643719417198</v>
+        <v>9.411494225879903</v>
       </c>
       <c r="F174" t="n">
-        <v>23872900</v>
+        <v>37702000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46085</v>
+        <v>46097</v>
       </c>
       <c r="B175" t="n">
-        <v>9.441214561462402</v>
+        <v>9.748327255249023</v>
       </c>
       <c r="C175" t="n">
-        <v>9.461028687209016</v>
+        <v>9.92665061436368</v>
       </c>
       <c r="D175" t="n">
-        <v>9.035034431551976</v>
+        <v>9.480842216577038</v>
       </c>
       <c r="E175" t="n">
-        <v>9.163823414536418</v>
+        <v>9.58981802260913</v>
       </c>
       <c r="F175" t="n">
-        <v>17524500</v>
+        <v>22733300</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46086</v>
+        <v>46098</v>
       </c>
       <c r="B176" t="n">
-        <v>9.074662208557129</v>
+        <v>8.955780029296875</v>
       </c>
       <c r="C176" t="n">
-        <v>9.500656486291655</v>
+        <v>9.837488805229597</v>
       </c>
       <c r="D176" t="n">
-        <v>9.044941963186449</v>
+        <v>8.955780029296875</v>
       </c>
       <c r="E176" t="n">
-        <v>9.371867496632623</v>
+        <v>9.787954434484694</v>
       </c>
       <c r="F176" t="n">
-        <v>20521200</v>
+        <v>22442400</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46087</v>
+        <v>46099</v>
       </c>
       <c r="B177" t="n">
-        <v>9.243078231811523</v>
+        <v>8.767550468444824</v>
       </c>
       <c r="C177" t="n">
-        <v>9.391680399030671</v>
+        <v>9.124196233698045</v>
       </c>
       <c r="D177" t="n">
-        <v>9.015221449436892</v>
+        <v>8.767550468444824</v>
       </c>
       <c r="E177" t="n">
-        <v>9.064754875316916</v>
+        <v>8.995407248936999</v>
       </c>
       <c r="F177" t="n">
-        <v>18677300</v>
+        <v>23534100</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46090</v>
+        <v>46100</v>
       </c>
       <c r="B178" t="n">
-        <v>9.431308746337891</v>
+        <v>8.688295364379883</v>
       </c>
       <c r="C178" t="n">
-        <v>9.431308746337891</v>
+        <v>8.817083397094507</v>
       </c>
       <c r="D178" t="n">
-        <v>9.064754966566955</v>
+        <v>8.361368916999025</v>
       </c>
       <c r="E178" t="n">
-        <v>9.134103464118251</v>
+        <v>8.628853934458961</v>
       </c>
       <c r="F178" t="n">
-        <v>16425800</v>
+        <v>23104500</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46091</v>
+        <v>46101</v>
       </c>
       <c r="B179" t="n">
-        <v>10.0455322265625</v>
+        <v>8.262301445007324</v>
       </c>
       <c r="C179" t="n">
-        <v>10.25357582413239</v>
+        <v>8.698201816984595</v>
       </c>
       <c r="D179" t="n">
-        <v>9.510563110638433</v>
+        <v>8.192953894753773</v>
       </c>
       <c r="E179" t="n">
-        <v>9.55019041756653</v>
+        <v>8.688295698940884</v>
       </c>
       <c r="F179" t="n">
-        <v>21417000</v>
+        <v>28291600</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46092</v>
+        <v>46104</v>
       </c>
       <c r="B180" t="n">
-        <v>9.946463584899902</v>
+        <v>8.678388595581055</v>
       </c>
       <c r="C180" t="n">
-        <v>10.21394861789357</v>
+        <v>8.797270514656061</v>
       </c>
       <c r="D180" t="n">
-        <v>9.867208970262416</v>
+        <v>8.50006524457379</v>
       </c>
       <c r="E180" t="n">
-        <v>9.90683627758116</v>
+        <v>8.509972307360751</v>
       </c>
       <c r="F180" t="n">
-        <v>13112300</v>
+        <v>20111900</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="B181" t="n">
-        <v>9.31242561340332</v>
+        <v>8.609040260314941</v>
       </c>
       <c r="C181" t="n">
-        <v>9.896929098067334</v>
+        <v>8.727923126381356</v>
       </c>
       <c r="D181" t="n">
-        <v>9.243078062609122</v>
+        <v>8.430717850794371</v>
       </c>
       <c r="E181" t="n">
-        <v>9.817674484362673</v>
+        <v>8.599134142134012</v>
       </c>
       <c r="F181" t="n">
-        <v>14948600</v>
+        <v>19212700</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46094</v>
+        <v>46106</v>
       </c>
       <c r="B182" t="n">
-        <v>9.252985000610352</v>
+        <v>8.807177543640137</v>
       </c>
       <c r="C182" t="n">
-        <v>10.23376154055783</v>
+        <v>9.084568687083829</v>
       </c>
       <c r="D182" t="n">
-        <v>9.064754587010629</v>
+        <v>8.737829049187084</v>
       </c>
       <c r="E182" t="n">
-        <v>9.411494225879903</v>
+        <v>8.817083661599568</v>
       </c>
       <c r="F182" t="n">
-        <v>37702000</v>
+        <v>17871200</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46097</v>
+        <v>46107</v>
       </c>
       <c r="B183" t="n">
-        <v>9.748327255249023</v>
+        <v>8.361369132995605</v>
       </c>
       <c r="C183" t="n">
-        <v>9.92665061436368</v>
+        <v>8.817083624863415</v>
       </c>
       <c r="D183" t="n">
-        <v>9.480842216577038</v>
+        <v>8.361369132995605</v>
       </c>
       <c r="E183" t="n">
-        <v>9.58981802260913</v>
+        <v>8.648667337991213</v>
       </c>
       <c r="F183" t="n">
-        <v>22733300</v>
+        <v>15274300</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="B184" t="n">
-        <v>8.955780029296875</v>
+        <v>8.014630317687988</v>
       </c>
       <c r="C184" t="n">
-        <v>9.837488805229597</v>
+        <v>8.371276066556085</v>
       </c>
       <c r="D184" t="n">
-        <v>8.955780029296875</v>
+        <v>8.00472325513317</v>
       </c>
       <c r="E184" t="n">
-        <v>9.787954434484694</v>
+        <v>8.331648761126296</v>
       </c>
       <c r="F184" t="n">
-        <v>22442400</v>
+        <v>22237700</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46099</v>
+        <v>46111</v>
       </c>
       <c r="B185" t="n">
-        <v>8.767550468444824</v>
+        <v>7.925468921661377</v>
       </c>
       <c r="C185" t="n">
-        <v>9.124196233698045</v>
+        <v>8.242487376195186</v>
       </c>
       <c r="D185" t="n">
-        <v>8.767550468444824</v>
+        <v>7.846214308027925</v>
       </c>
       <c r="E185" t="n">
-        <v>8.995407248936999</v>
+        <v>8.232581258083144</v>
       </c>
       <c r="F185" t="n">
-        <v>23534100</v>
+        <v>17213200</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46100</v>
+        <v>46112</v>
       </c>
       <c r="B186" t="n">
         <v>8.688295364379883</v>
       </c>
       <c r="C186" t="n">
-        <v>8.817083397094507</v>
+        <v>8.757642911963062</v>
       </c>
       <c r="D186" t="n">
-        <v>8.361368916999025</v>
+        <v>8.173139454363479</v>
       </c>
       <c r="E186" t="n">
-        <v>8.628853934458961</v>
+        <v>8.173139454363479</v>
       </c>
       <c r="F186" t="n">
-        <v>23104500</v>
+        <v>27630300</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46101</v>
+        <v>46113</v>
       </c>
       <c r="B187" t="n">
-        <v>8.262301445007324</v>
+        <v>8.757643699645996</v>
       </c>
       <c r="C187" t="n">
-        <v>8.698201816984595</v>
+        <v>8.935967060658106</v>
       </c>
       <c r="D187" t="n">
-        <v>8.192953894753773</v>
+        <v>8.638761773901111</v>
       </c>
       <c r="E187" t="n">
-        <v>8.688295698940884</v>
+        <v>8.727923454407165</v>
       </c>
       <c r="F187" t="n">
-        <v>28291600</v>
+        <v>19365500</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46104</v>
+        <v>46114</v>
       </c>
       <c r="B188" t="n">
-        <v>8.678388595581055</v>
+        <v>8.668481826782227</v>
       </c>
       <c r="C188" t="n">
-        <v>8.797270514656061</v>
+        <v>8.797270813012021</v>
       </c>
       <c r="D188" t="n">
-        <v>8.50006524457379</v>
+        <v>8.371276546620356</v>
       </c>
       <c r="E188" t="n">
-        <v>8.509972307360751</v>
+        <v>8.509972595973107</v>
       </c>
       <c r="F188" t="n">
-        <v>20111900</v>
+        <v>14359700</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46105</v>
+        <v>46118</v>
       </c>
       <c r="B189" t="n">
-        <v>8.609040260314941</v>
+        <v>8.737829208374023</v>
       </c>
       <c r="C189" t="n">
-        <v>8.727923126381356</v>
+        <v>8.916152561945582</v>
       </c>
       <c r="D189" t="n">
-        <v>8.430717850794371</v>
+        <v>8.579319980661314</v>
       </c>
       <c r="E189" t="n">
-        <v>8.599134142134012</v>
+        <v>8.718016027304696</v>
       </c>
       <c r="F189" t="n">
-        <v>19212700</v>
+        <v>13342900</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46106</v>
+        <v>46119</v>
       </c>
       <c r="B190" t="n">
-        <v>8.807177543640137</v>
+        <v>8.698202133178711</v>
       </c>
       <c r="C190" t="n">
-        <v>9.084568687083829</v>
+        <v>8.856711365114338</v>
       </c>
       <c r="D190" t="n">
-        <v>8.737829049187084</v>
+        <v>8.500065593259176</v>
       </c>
       <c r="E190" t="n">
-        <v>8.817083661599568</v>
+        <v>8.658574825194803</v>
       </c>
       <c r="F190" t="n">
-        <v>17871200</v>
+        <v>12038500</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46107</v>
+        <v>46120</v>
       </c>
       <c r="B191" t="n">
-        <v>8.361369132995605</v>
+        <v>8.866618156433105</v>
       </c>
       <c r="C191" t="n">
-        <v>8.817083624863415</v>
+        <v>9.431308458875774</v>
       </c>
       <c r="D191" t="n">
-        <v>8.361369132995605</v>
+        <v>8.866618156433105</v>
       </c>
       <c r="E191" t="n">
-        <v>8.648667337991213</v>
+        <v>9.252985106021297</v>
       </c>
       <c r="F191" t="n">
-        <v>15274300</v>
+        <v>18316300</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46108</v>
+        <v>46121</v>
       </c>
       <c r="B192" t="n">
-        <v>8.014630317687988</v>
+        <v>9.144009590148926</v>
       </c>
       <c r="C192" t="n">
-        <v>8.371276066556085</v>
+        <v>9.163823716548555</v>
       </c>
       <c r="D192" t="n">
-        <v>8.00472325513317</v>
+        <v>8.866618434080962</v>
       </c>
       <c r="E192" t="n">
-        <v>8.331648761126296</v>
+        <v>8.94587305010038</v>
       </c>
       <c r="F192" t="n">
-        <v>22237700</v>
+        <v>14711600</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46111</v>
+        <v>46122</v>
       </c>
       <c r="B193" t="n">
-        <v>7.925468921661377</v>
+        <v>9.064754486083984</v>
       </c>
       <c r="C193" t="n">
-        <v>8.242487376195186</v>
+        <v>9.38177387788291</v>
       </c>
       <c r="D193" t="n">
-        <v>7.846214308027925</v>
+        <v>8.945872568455448</v>
       </c>
       <c r="E193" t="n">
-        <v>8.232581258083144</v>
+        <v>9.262891960254375</v>
       </c>
       <c r="F193" t="n">
-        <v>17213200</v>
+        <v>13301800</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46112</v>
+        <v>46125</v>
       </c>
       <c r="B194" t="n">
-        <v>8.688295364379883</v>
+        <v>9.12419605255127</v>
       </c>
       <c r="C194" t="n">
-        <v>8.757642911963062</v>
+        <v>9.282705278405746</v>
       </c>
       <c r="D194" t="n">
-        <v>8.173139454363479</v>
+        <v>8.836897844492654</v>
       </c>
       <c r="E194" t="n">
-        <v>8.173139454363479</v>
+        <v>8.866618088142991</v>
       </c>
       <c r="F194" t="n">
-        <v>27630300</v>
+        <v>14389900</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="B195" t="n">
-        <v>8.757643699645996</v>
+        <v>9.163823127746582</v>
       </c>
       <c r="C195" t="n">
-        <v>8.935967060658106</v>
+        <v>9.3817737801908</v>
       </c>
       <c r="D195" t="n">
-        <v>8.638761773901111</v>
+        <v>9.074661454256242</v>
       </c>
       <c r="E195" t="n">
-        <v>8.727923454407165</v>
+        <v>9.21335749577338</v>
       </c>
       <c r="F195" t="n">
-        <v>19365500</v>
+        <v>13395600</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46114</v>
+        <v>46127</v>
       </c>
       <c r="B196" t="n">
-        <v>8.668481826782227</v>
+        <v>9.302519798278809</v>
       </c>
       <c r="C196" t="n">
-        <v>8.797270813012021</v>
+        <v>9.332240043188708</v>
       </c>
       <c r="D196" t="n">
-        <v>8.371276546620356</v>
+        <v>9.094476194330415</v>
       </c>
       <c r="E196" t="n">
-        <v>8.509972595973107</v>
+        <v>9.144009620917062</v>
       </c>
       <c r="F196" t="n">
-        <v>14359700</v>
+        <v>12868500</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46118</v>
+        <v>46128</v>
       </c>
       <c r="B197" t="n">
-        <v>8.737829208374023</v>
+        <v>9.163823127746582</v>
       </c>
       <c r="C197" t="n">
-        <v>8.916152561945582</v>
+        <v>9.352052592501028</v>
       </c>
       <c r="D197" t="n">
-        <v>8.579319980661314</v>
+        <v>9.094475579382756</v>
       </c>
       <c r="E197" t="n">
-        <v>8.718016027304696</v>
+        <v>9.352052592501028</v>
       </c>
       <c r="F197" t="n">
-        <v>13342900</v>
+        <v>12966700</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46119</v>
+        <v>46129</v>
       </c>
       <c r="B198" t="n">
-        <v>8.698202133178711</v>
+        <v>9.203451156616211</v>
       </c>
       <c r="C198" t="n">
-        <v>8.856711365114338</v>
+        <v>9.669072741003538</v>
       </c>
       <c r="D198" t="n">
-        <v>8.500065593259176</v>
+        <v>9.124196539459588</v>
       </c>
       <c r="E198" t="n">
-        <v>8.658574825194803</v>
+        <v>9.292612837114801</v>
       </c>
       <c r="F198" t="n">
-        <v>12038500</v>
+        <v>18950900</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46120</v>
+        <v>46132</v>
       </c>
       <c r="B199" t="n">
-        <v>8.866618156433105</v>
+        <v>9.26289176940918</v>
       </c>
       <c r="C199" t="n">
-        <v>9.431308458875774</v>
+        <v>9.322332254604035</v>
       </c>
       <c r="D199" t="n">
-        <v>8.866618156433105</v>
+        <v>9.035034056723626</v>
       </c>
       <c r="E199" t="n">
-        <v>9.252985106021297</v>
+        <v>9.18363715928972</v>
       </c>
       <c r="F199" t="n">
-        <v>18316300</v>
+        <v>14635000</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46121</v>
+        <v>46134</v>
       </c>
       <c r="B200" t="n">
-        <v>9.144009590148926</v>
+        <v>8.866618156433105</v>
       </c>
       <c r="C200" t="n">
-        <v>9.163823716548555</v>
+        <v>9.233170980242125</v>
       </c>
       <c r="D200" t="n">
-        <v>8.866618434080962</v>
+        <v>8.866618156433105</v>
       </c>
       <c r="E200" t="n">
-        <v>8.94587305010038</v>
+        <v>9.193543673473298</v>
       </c>
       <c r="F200" t="n">
-        <v>14711600</v>
+        <v>12795800</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46122</v>
+        <v>46135</v>
       </c>
       <c r="B201" t="n">
-        <v>9.064754486083984</v>
+        <v>8.569413185119629</v>
       </c>
       <c r="C201" t="n">
-        <v>9.38177387788291</v>
+        <v>8.935966966629591</v>
       </c>
       <c r="D201" t="n">
-        <v>8.945872568455448</v>
+        <v>8.549600003432079</v>
       </c>
       <c r="E201" t="n">
-        <v>9.262891960254375</v>
+        <v>8.896338713675389</v>
       </c>
       <c r="F201" t="n">
-        <v>13301800</v>
+        <v>12084000</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46125</v>
+        <v>46136</v>
       </c>
       <c r="B202" t="n">
-        <v>9.12419605255127</v>
+        <v>8.648667335510254</v>
       </c>
       <c r="C202" t="n">
-        <v>9.282705278405746</v>
+        <v>8.678388523624706</v>
       </c>
       <c r="D202" t="n">
-        <v>8.836897844492654</v>
+        <v>8.450530805361414</v>
       </c>
       <c r="E202" t="n">
-        <v>8.866618088142991</v>
+        <v>8.628854154890121</v>
       </c>
       <c r="F202" t="n">
-        <v>14389900</v>
+        <v>9917800</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46126</v>
+        <v>46139</v>
       </c>
       <c r="B203" t="n">
-        <v>9.163823127746582</v>
+        <v>8.529999732971191</v>
       </c>
       <c r="C203" t="n">
-        <v>9.3817737801908</v>
+        <v>8.770000457763672</v>
       </c>
       <c r="D203" t="n">
-        <v>9.074661454256242</v>
+        <v>8.470000267028809</v>
       </c>
       <c r="E203" t="n">
-        <v>9.21335749577338</v>
+        <v>8.689999580383301</v>
       </c>
       <c r="F203" t="n">
-        <v>13395600</v>
+        <v>8331300</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46127</v>
+        <v>46140</v>
       </c>
       <c r="B204" t="n">
-        <v>9.302519798278809</v>
+        <v>8.539999961853027</v>
       </c>
       <c r="C204" t="n">
-        <v>9.332240043188708</v>
+        <v>8.609999656677246</v>
       </c>
       <c r="D204" t="n">
-        <v>9.094476194330415</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="E204" t="n">
-        <v>9.144009620917062</v>
+        <v>8.5</v>
       </c>
       <c r="F204" t="n">
-        <v>12868500</v>
+        <v>10183500</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46128</v>
+        <v>46141</v>
       </c>
       <c r="B205" t="n">
-        <v>9.163823127746582</v>
+        <v>8.079999923706055</v>
       </c>
       <c r="C205" t="n">
-        <v>9.352052592501028</v>
+        <v>8.579999923706055</v>
       </c>
       <c r="D205" t="n">
-        <v>9.094475579382756</v>
+        <v>8.079999923706055</v>
       </c>
       <c r="E205" t="n">
-        <v>9.352052592501028</v>
+        <v>8.529999732971191</v>
       </c>
       <c r="F205" t="n">
-        <v>12966700</v>
+        <v>14208700</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46129</v>
+        <v>46142</v>
       </c>
       <c r="B206" t="n">
-        <v>9.203451156616211</v>
+        <v>8.229999542236328</v>
       </c>
       <c r="C206" t="n">
-        <v>9.669072741003538</v>
+        <v>8.350000381469727</v>
       </c>
       <c r="D206" t="n">
-        <v>9.124196539459588</v>
+        <v>8.079999923706055</v>
       </c>
       <c r="E206" t="n">
-        <v>9.292612837114801</v>
+        <v>8.289999961853027</v>
       </c>
       <c r="F206" t="n">
-        <v>18950900</v>
+        <v>17525600</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="B207" t="n">
-        <v>9.26289176940918</v>
+        <v>8</v>
       </c>
       <c r="C207" t="n">
-        <v>9.322332254604035</v>
+        <v>8.340000152587891</v>
       </c>
       <c r="D207" t="n">
-        <v>9.035034056723626</v>
+        <v>7.989999771118164</v>
       </c>
       <c r="E207" t="n">
-        <v>9.18363715928972</v>
+        <v>8.25</v>
       </c>
       <c r="F207" t="n">
-        <v>14635000</v>
+        <v>14398300</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="B208" t="n">
-        <v>8.866618156433105</v>
+        <v>8</v>
       </c>
       <c r="C208" t="n">
-        <v>9.233170980242125</v>
+        <v>8.170000076293945</v>
       </c>
       <c r="D208" t="n">
-        <v>8.866618156433105</v>
+        <v>8</v>
       </c>
       <c r="E208" t="n">
-        <v>9.193543673473298</v>
+        <v>8.050000190734863</v>
       </c>
       <c r="F208" t="n">
-        <v>12795800</v>
+        <v>15252400</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46135</v>
+        <v>46148</v>
       </c>
       <c r="B209" t="n">
-        <v>8.569413185119629</v>
+        <v>8.029999732971191</v>
       </c>
       <c r="C209" t="n">
-        <v>8.935966966629591</v>
+        <v>8.319999694824219</v>
       </c>
       <c r="D209" t="n">
-        <v>8.549600003432079</v>
+        <v>8.020000457763672</v>
       </c>
       <c r="E209" t="n">
-        <v>8.896338713675389</v>
+        <v>8.220000267028809</v>
       </c>
       <c r="F209" t="n">
-        <v>12084000</v>
+        <v>11485200</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46136</v>
+        <v>46149</v>
       </c>
       <c r="B210" t="n">
-        <v>8.648667335510254</v>
+        <v>7.940000057220459</v>
       </c>
       <c r="C210" t="n">
-        <v>8.678388523624706</v>
+        <v>8.170000076293945</v>
       </c>
       <c r="D210" t="n">
-        <v>8.450530805361414</v>
+        <v>7.900000095367432</v>
       </c>
       <c r="E210" t="n">
-        <v>8.628854154890121</v>
+        <v>8.050000190734863</v>
       </c>
       <c r="F210" t="n">
-        <v>9917800</v>
+        <v>15526800</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46139</v>
+        <v>46150</v>
       </c>
       <c r="B211" t="n">
-        <v>8.529999732971191</v>
+        <v>7.150000095367432</v>
       </c>
       <c r="C211" t="n">
-        <v>8.770000457763672</v>
+        <v>7.849999904632568</v>
       </c>
       <c r="D211" t="n">
-        <v>8.470000267028809</v>
+        <v>7.150000095367432</v>
       </c>
       <c r="E211" t="n">
-        <v>8.689999580383301</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="F211" t="n">
-        <v>8331300</v>
+        <v>35215100</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>46140</v>
+        <v>46153</v>
       </c>
       <c r="B212" t="n">
-        <v>8.539999961853027</v>
+        <v>6.929999828338623</v>
       </c>
       <c r="C212" t="n">
-        <v>8.609999656677246</v>
+        <v>7.210000038146973</v>
       </c>
       <c r="D212" t="n">
-        <v>8.399999618530273</v>
+        <v>6.900000095367432</v>
       </c>
       <c r="E212" t="n">
-        <v>8.5</v>
+        <v>7.119999885559082</v>
       </c>
       <c r="F212" t="n">
-        <v>10183500</v>
+        <v>18515700</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>46141</v>
+        <v>46154</v>
       </c>
       <c r="B213" t="n">
-        <v>8.079999923706055</v>
+        <v>7.159999847412109</v>
       </c>
       <c r="C213" t="n">
-        <v>8.579999923706055</v>
+        <v>7.199999809265137</v>
       </c>
       <c r="D213" t="n">
-        <v>8.079999923706055</v>
+        <v>6.800000190734863</v>
       </c>
       <c r="E213" t="n">
-        <v>8.529999732971191</v>
+        <v>6.929999828338623</v>
       </c>
       <c r="F213" t="n">
-        <v>14208700</v>
+        <v>17784300</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>46142</v>
+        <v>46155</v>
       </c>
       <c r="B214" t="n">
-        <v>8.229999542236328</v>
+        <v>6.960000038146973</v>
       </c>
       <c r="C214" t="n">
-        <v>8.350000381469727</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="D214" t="n">
-        <v>8.079999923706055</v>
+        <v>6.960000038146973</v>
       </c>
       <c r="E214" t="n">
-        <v>8.289999961853027</v>
+        <v>7.119999885559082</v>
       </c>
       <c r="F214" t="n">
-        <v>17525600</v>
+        <v>22615000</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="B215" t="n">
-        <v>8</v>
+        <v>6.909999847412109</v>
       </c>
       <c r="C215" t="n">
-        <v>8.340000152587891</v>
+        <v>7.130000114440918</v>
       </c>
       <c r="D215" t="n">
-        <v>7.989999771118164</v>
+        <v>6.829999923706055</v>
       </c>
       <c r="E215" t="n">
-        <v>8.25</v>
+        <v>7.090000152587891</v>
       </c>
       <c r="F215" t="n">
-        <v>14398300</v>
+        <v>20866400</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>46147</v>
+        <v>46157</v>
       </c>
       <c r="B216" t="n">
-        <v>8</v>
+        <v>6.789999961853027</v>
       </c>
       <c r="C216" t="n">
-        <v>8.170000076293945</v>
+        <v>6.840000152587891</v>
       </c>
       <c r="D216" t="n">
-        <v>8</v>
+        <v>6.599999904632568</v>
       </c>
       <c r="E216" t="n">
-        <v>8.050000190734863</v>
+        <v>6.820000171661377</v>
       </c>
       <c r="F216" t="n">
-        <v>15252400</v>
+        <v>17594900</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="B217" t="n">
-        <v>8.029999732971191</v>
+        <v>6.610000133514404</v>
       </c>
       <c r="C217" t="n">
-        <v>8.319999694824219</v>
+        <v>6.989999771118164</v>
       </c>
       <c r="D217" t="n">
-        <v>8.020000457763672</v>
+        <v>6.610000133514404</v>
       </c>
       <c r="E217" t="n">
-        <v>8.220000267028809</v>
+        <v>6.829999923706055</v>
       </c>
       <c r="F217" t="n">
-        <v>11485200</v>
+        <v>18028200</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="B218" t="n">
-        <v>7.940000057220459</v>
+        <v>6.489999771118164</v>
       </c>
       <c r="C218" t="n">
-        <v>8.170000076293945</v>
+        <v>6.670000076293945</v>
       </c>
       <c r="D218" t="n">
-        <v>7.900000095367432</v>
+        <v>6.340000152587891</v>
       </c>
       <c r="E218" t="n">
-        <v>8.050000190734863</v>
+        <v>6.510000228881836</v>
       </c>
       <c r="F218" t="n">
-        <v>15526800</v>
+        <v>18272100</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="B219" t="n">
-        <v>7.150000095367432</v>
+        <v>6.730000019073486</v>
       </c>
       <c r="C219" t="n">
-        <v>7.849999904632568</v>
+        <v>6.800000190734863</v>
       </c>
       <c r="D219" t="n">
-        <v>7.150000095367432</v>
+        <v>6.489999771118164</v>
       </c>
       <c r="E219" t="n">
-        <v>7.599999904632568</v>
+        <v>6.53000020980835</v>
       </c>
       <c r="F219" t="n">
-        <v>35215100</v>
+        <v>21093700</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="B220" t="n">
-        <v>6.929999828338623</v>
+        <v>6.769999980926514</v>
       </c>
       <c r="C220" t="n">
-        <v>7.210000038146973</v>
+        <v>6.789999961853027</v>
       </c>
       <c r="D220" t="n">
-        <v>6.900000095367432</v>
+        <v>6.46999979019165</v>
       </c>
       <c r="E220" t="n">
-        <v>7.119999885559082</v>
+        <v>6.659999847412109</v>
       </c>
       <c r="F220" t="n">
-        <v>18515700</v>
+        <v>17378400</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="B221" t="n">
-        <v>7.159999847412109</v>
+        <v>6.630000114440918</v>
       </c>
       <c r="C221" t="n">
-        <v>7.199999809265137</v>
+        <v>6.880000114440918</v>
       </c>
       <c r="D221" t="n">
-        <v>6.800000190734863</v>
+        <v>6.610000133514404</v>
       </c>
       <c r="E221" t="n">
-        <v>6.929999828338623</v>
+        <v>6.699999809265137</v>
       </c>
       <c r="F221" t="n">
-        <v>17784300</v>
+        <v>13376800</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>46155</v>
+        <v>46167</v>
       </c>
       <c r="B222" t="n">
-        <v>6.960000038146973</v>
+        <v>6.769999980926514</v>
       </c>
       <c r="C222" t="n">
-        <v>7.400000095367432</v>
+        <v>6.829999923706055</v>
       </c>
       <c r="D222" t="n">
-        <v>6.960000038146973</v>
+        <v>6.670000076293945</v>
       </c>
       <c r="E222" t="n">
-        <v>7.119999885559082</v>
+        <v>6.739999771118164</v>
       </c>
       <c r="F222" t="n">
-        <v>22615000</v>
+        <v>10045800</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="B223" t="n">
-        <v>6.909999847412109</v>
+        <v>6.650000095367432</v>
       </c>
       <c r="C223" t="n">
-        <v>7.130000114440918</v>
+        <v>6.78000020980835</v>
       </c>
       <c r="D223" t="n">
-        <v>6.829999923706055</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="E223" t="n">
-        <v>7.090000152587891</v>
+        <v>6.769999980926514</v>
       </c>
       <c r="F223" t="n">
-        <v>20866400</v>
+        <v>10894700</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="B224" t="n">
-        <v>6.789999961853027</v>
+        <v>6.599999904632568</v>
       </c>
       <c r="C224" t="n">
-        <v>6.840000152587891</v>
+        <v>6.829999923706055</v>
       </c>
       <c r="D224" t="n">
-        <v>6.599999904632568</v>
+        <v>6.590000152587891</v>
       </c>
       <c r="E224" t="n">
-        <v>6.820000171661377</v>
+        <v>6.739999771118164</v>
       </c>
       <c r="F224" t="n">
-        <v>17594900</v>
+        <v>13503200</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>46160</v>
+        <v>46170</v>
       </c>
       <c r="B225" t="n">
-        <v>6.610000133514404</v>
+        <v>6.349999904632568</v>
       </c>
       <c r="C225" t="n">
-        <v>6.989999771118164</v>
+        <v>6.710000038146973</v>
       </c>
       <c r="D225" t="n">
-        <v>6.610000133514404</v>
+        <v>6.349999904632568</v>
       </c>
       <c r="E225" t="n">
-        <v>6.829999923706055</v>
+        <v>6.650000095367432</v>
       </c>
       <c r="F225" t="n">
-        <v>18028200</v>
+        <v>17829300</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="B226" t="n">
-        <v>6.489999771118164</v>
+        <v>5.980000019073486</v>
       </c>
       <c r="C226" t="n">
-        <v>6.670000076293945</v>
+        <v>6.429999828338623</v>
       </c>
       <c r="D226" t="n">
-        <v>6.340000152587891</v>
+        <v>5.980000019073486</v>
       </c>
       <c r="E226" t="n">
-        <v>6.510000228881836</v>
+        <v>6.380000114440918</v>
       </c>
       <c r="F226" t="n">
-        <v>18272100</v>
+        <v>19948000</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>46162</v>
+        <v>46174</v>
       </c>
       <c r="B227" t="n">
-        <v>6.730000019073486</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="C227" t="n">
-        <v>6.800000190734863</v>
+        <v>6.070000171661377</v>
       </c>
       <c r="D227" t="n">
-        <v>6.489999771118164</v>
+        <v>5.760000228881836</v>
       </c>
       <c r="E227" t="n">
-        <v>6.53000020980835</v>
+        <v>5.980000019073486</v>
       </c>
       <c r="F227" t="n">
-        <v>21093700</v>
+        <v>19869200</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>46163</v>
+        <v>46175</v>
       </c>
       <c r="B228" t="n">
-        <v>6.769999980926514</v>
+        <v>5.679999828338623</v>
       </c>
       <c r="C228" t="n">
-        <v>6.789999961853027</v>
+        <v>5.929999828338623</v>
       </c>
       <c r="D228" t="n">
-        <v>6.46999979019165</v>
+        <v>5.679999828338623</v>
       </c>
       <c r="E228" t="n">
-        <v>6.659999847412109</v>
+        <v>5.849999904632568</v>
       </c>
       <c r="F228" t="n">
-        <v>17378400</v>
+        <v>18461700</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>46164</v>
+        <v>46176</v>
       </c>
       <c r="B229" t="n">
-        <v>6.630000114440918</v>
+        <v>5.340000152587891</v>
       </c>
       <c r="C229" t="n">
-        <v>6.880000114440918</v>
+        <v>5.550000190734863</v>
       </c>
       <c r="D229" t="n">
-        <v>6.610000133514404</v>
+        <v>5.320000171661377</v>
       </c>
       <c r="E229" t="n">
-        <v>6.699999809265137</v>
+        <v>5.550000190734863</v>
       </c>
       <c r="F229" t="n">
-        <v>13376800</v>
+        <v>23074300</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>46167</v>
+        <v>46178</v>
       </c>
       <c r="B230" t="n">
-        <v>6.769999980926514</v>
+        <v>5.440000057220459</v>
       </c>
       <c r="C230" t="n">
-        <v>6.829999923706055</v>
+        <v>5.670000076293945</v>
       </c>
       <c r="D230" t="n">
-        <v>6.670000076293945</v>
+        <v>5.289999961853027</v>
       </c>
       <c r="E230" t="n">
-        <v>6.739999771118164</v>
+        <v>5.440000057220459</v>
       </c>
       <c r="F230" t="n">
-        <v>10045800</v>
+        <v>27759100</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>46168</v>
+        <v>46181</v>
       </c>
       <c r="B231" t="n">
-        <v>6.650000095367432</v>
+        <v>5.340000152587891</v>
       </c>
       <c r="C231" t="n">
-        <v>6.78000020980835</v>
+        <v>5.539999961853027</v>
       </c>
       <c r="D231" t="n">
-        <v>6.550000190734863</v>
+        <v>5.340000152587891</v>
       </c>
       <c r="E231" t="n">
-        <v>6.769999980926514</v>
+        <v>5.449999809265137</v>
       </c>
       <c r="F231" t="n">
-        <v>10894700</v>
+        <v>17634500</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>46169</v>
+        <v>46182</v>
       </c>
       <c r="B232" t="n">
-        <v>6.599999904632568</v>
+        <v>5.489999771118164</v>
       </c>
       <c r="C232" t="n">
-        <v>6.829999923706055</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="D232" t="n">
-        <v>6.590000152587891</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="E232" t="n">
-        <v>6.739999771118164</v>
+        <v>5.46999979019165</v>
       </c>
       <c r="F232" t="n">
-        <v>13503200</v>
+        <v>24632800</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>46170</v>
+        <v>46183</v>
       </c>
       <c r="B233" t="n">
-        <v>6.349999904632568</v>
+        <v>5.119999885559082</v>
       </c>
       <c r="C233" t="n">
-        <v>6.710000038146973</v>
+        <v>5.46999979019165</v>
       </c>
       <c r="D233" t="n">
-        <v>6.349999904632568</v>
+        <v>5.119999885559082</v>
       </c>
       <c r="E233" t="n">
-        <v>6.650000095367432</v>
+        <v>5.460000038146973</v>
       </c>
       <c r="F233" t="n">
-        <v>17829300</v>
+        <v>23198500</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>46171</v>
+        <v>46184</v>
       </c>
       <c r="B234" t="n">
-        <v>5.980000019073486</v>
+        <v>5.329999923706055</v>
       </c>
       <c r="C234" t="n">
-        <v>6.429999828338623</v>
+        <v>5.380000114440918</v>
       </c>
       <c r="D234" t="n">
-        <v>5.980000019073486</v>
+        <v>5.099999904632568</v>
       </c>
       <c r="E234" t="n">
-        <v>6.380000114440918</v>
+        <v>5.159999847412109</v>
       </c>
       <c r="F234" t="n">
-        <v>19948000</v>
+        <v>28878200</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="B235" t="n">
-        <v>5.820000171661377</v>
+        <v>5.21999979019165</v>
       </c>
       <c r="C235" t="n">
-        <v>6.070000171661377</v>
+        <v>5.440000057220459</v>
       </c>
       <c r="D235" t="n">
-        <v>5.760000228881836</v>
+        <v>5.190000057220459</v>
       </c>
       <c r="E235" t="n">
-        <v>5.980000019073486</v>
+        <v>5.230000019073486</v>
       </c>
       <c r="F235" t="n">
-        <v>19869200</v>
+        <v>16254200</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>46175</v>
+        <v>46188</v>
       </c>
       <c r="B236" t="n">
-        <v>5.679999828338623</v>
+        <v>5.349999904632568</v>
       </c>
       <c r="C236" t="n">
-        <v>5.929999828338623</v>
+        <v>5.46999979019165</v>
       </c>
       <c r="D236" t="n">
-        <v>5.679999828338623</v>
+        <v>5.260000228881836</v>
       </c>
       <c r="E236" t="n">
-        <v>5.849999904632568</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="F236" t="n">
-        <v>18461700</v>
+        <v>18145200</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>46176</v>
+        <v>46189</v>
       </c>
       <c r="B237" t="n">
-        <v>5.340000152587891</v>
+        <v>5</v>
       </c>
       <c r="C237" t="n">
-        <v>5.550000190734863</v>
+        <v>5.300000190734863</v>
       </c>
       <c r="D237" t="n">
-        <v>5.320000171661377</v>
+        <v>4.989999771118164</v>
       </c>
       <c r="E237" t="n">
-        <v>5.550000190734863</v>
+        <v>5.289999961853027</v>
       </c>
       <c r="F237" t="n">
-        <v>23074300</v>
+        <v>25995600</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>46178</v>
+        <v>46190</v>
       </c>
       <c r="B238" t="n">
-        <v>5.440000057220459</v>
+        <v>4.739999771118164</v>
       </c>
       <c r="C238" t="n">
-        <v>5.670000076293945</v>
+        <v>5.119999885559082</v>
       </c>
       <c r="D238" t="n">
-        <v>5.289999961853027</v>
+        <v>4.739999771118164</v>
       </c>
       <c r="E238" t="n">
-        <v>5.440000057220459</v>
+        <v>5.03000020980835</v>
       </c>
       <c r="F238" t="n">
-        <v>27759100</v>
+        <v>28655600</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>46181</v>
+        <v>46191</v>
       </c>
       <c r="B239" t="n">
-        <v>5.340000152587891</v>
+        <v>4.5</v>
       </c>
       <c r="C239" t="n">
-        <v>5.539999961853027</v>
+        <v>4.800000190734863</v>
       </c>
       <c r="D239" t="n">
-        <v>5.340000152587891</v>
+        <v>4.46999979019165</v>
       </c>
       <c r="E239" t="n">
-        <v>5.449999809265137</v>
+        <v>4.78000020980835</v>
       </c>
       <c r="F239" t="n">
-        <v>17634500</v>
+        <v>30716200</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46182</v>
+        <v>46192</v>
       </c>
       <c r="B240" t="n">
-        <v>5.489999771118164</v>
+        <v>4.619999885559082</v>
       </c>
       <c r="C240" t="n">
-        <v>5.659999847412109</v>
+        <v>4.650000095367432</v>
       </c>
       <c r="D240" t="n">
-        <v>5.460000038146973</v>
+        <v>4.46999979019165</v>
       </c>
       <c r="E240" t="n">
-        <v>5.46999979019165</v>
+        <v>4.480000019073486</v>
       </c>
       <c r="F240" t="n">
-        <v>24632800</v>
+        <v>21086800</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="B241" t="n">
-        <v>5.119999885559082</v>
+        <v>4.659999847412109</v>
       </c>
       <c r="C241" t="n">
-        <v>5.46999979019165</v>
+        <v>4.840000152587891</v>
       </c>
       <c r="D241" t="n">
-        <v>5.119999885559082</v>
+        <v>4.559999942779541</v>
       </c>
       <c r="E241" t="n">
-        <v>5.460000038146973</v>
+        <v>4.630000114440918</v>
       </c>
       <c r="F241" t="n">
-        <v>23198500</v>
+        <v>21375500</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="B242" t="n">
-        <v>5.329999923706055</v>
+        <v>4.420000076293945</v>
       </c>
       <c r="C242" t="n">
-        <v>5.380000114440918</v>
+        <v>4.639999866485596</v>
       </c>
       <c r="D242" t="n">
-        <v>5.099999904632568</v>
+        <v>4.420000076293945</v>
       </c>
       <c r="E242" t="n">
-        <v>5.159999847412109</v>
+        <v>4.610000133514404</v>
       </c>
       <c r="F242" t="n">
-        <v>28878200</v>
+        <v>24418400</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>46185</v>
+        <v>46197</v>
       </c>
       <c r="B243" t="n">
-        <v>5.21999979019165</v>
+        <v>4.360000133514404</v>
       </c>
       <c r="C243" t="n">
-        <v>5.440000057220459</v>
+        <v>4.480000019073486</v>
       </c>
       <c r="D243" t="n">
-        <v>5.190000057220459</v>
+        <v>4.300000190734863</v>
       </c>
       <c r="E243" t="n">
-        <v>5.230000019073486</v>
+        <v>4.380000114440918</v>
       </c>
       <c r="F243" t="n">
-        <v>16254200</v>
+        <v>21608000</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>46188</v>
+        <v>46198</v>
       </c>
       <c r="B244" t="n">
-        <v>5.349999904632568</v>
+        <v>4.420000076293945</v>
       </c>
       <c r="C244" t="n">
-        <v>5.46999979019165</v>
+        <v>4.510000228881836</v>
       </c>
       <c r="D244" t="n">
-        <v>5.260000228881836</v>
+        <v>4.03000020980835</v>
       </c>
       <c r="E244" t="n">
-        <v>5.400000095367432</v>
+        <v>4.409999847412109</v>
       </c>
       <c r="F244" t="n">
-        <v>18145200</v>
+        <v>52346600</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>46189</v>
+        <v>46199</v>
       </c>
       <c r="B245" t="n">
-        <v>5</v>
+        <v>4.440000057220459</v>
       </c>
       <c r="C245" t="n">
-        <v>5.300000190734863</v>
+        <v>4.570000171661377</v>
       </c>
       <c r="D245" t="n">
-        <v>4.989999771118164</v>
+        <v>4.329999923706055</v>
       </c>
       <c r="E245" t="n">
-        <v>5.289999961853027</v>
+        <v>4.389999866485596</v>
       </c>
       <c r="F245" t="n">
-        <v>25995600</v>
+        <v>25874600</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>46190</v>
+        <v>46202</v>
       </c>
       <c r="B246" t="n">
-        <v>4.739999771118164</v>
+        <v>4.639999866485596</v>
       </c>
       <c r="C246" t="n">
-        <v>5.119999885559082</v>
+        <v>4.710000038146973</v>
       </c>
       <c r="D246" t="n">
-        <v>4.739999771118164</v>
+        <v>4.409999847412109</v>
       </c>
       <c r="E246" t="n">
-        <v>5.03000020980835</v>
+        <v>4.409999847412109</v>
       </c>
       <c r="F246" t="n">
-        <v>28655600</v>
+        <v>18574500</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>46191</v>
+        <v>46203</v>
       </c>
       <c r="B247" t="n">
-        <v>4.5</v>
+        <v>4.679999828338623</v>
       </c>
       <c r="C247" t="n">
-        <v>4.800000190734863</v>
+        <v>4.739999771118164</v>
       </c>
       <c r="D247" t="n">
-        <v>4.46999979019165</v>
+        <v>4.460000038146973</v>
       </c>
       <c r="E247" t="n">
-        <v>4.78000020980835</v>
+        <v>4.590000152587891</v>
       </c>
       <c r="F247" t="n">
-        <v>30716200</v>
+        <v>18658400</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>46192</v>
+        <v>46204</v>
       </c>
       <c r="B248" t="n">
-        <v>4.619999885559082</v>
+        <v>4.429999828338623</v>
       </c>
       <c r="C248" t="n">
-        <v>4.650000095367432</v>
+        <v>4.690000057220459</v>
       </c>
       <c r="D248" t="n">
-        <v>4.46999979019165</v>
+        <v>4.429999828338623</v>
       </c>
       <c r="E248" t="n">
-        <v>4.480000019073486</v>
+        <v>4.590000152587891</v>
       </c>
       <c r="F248" t="n">
-        <v>21086800</v>
+        <v>22221800</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>46195</v>
+        <v>46205</v>
       </c>
       <c r="B249" t="n">
-        <v>4.659999847412109</v>
+        <v>4.269999980926514</v>
       </c>
       <c r="C249" t="n">
-        <v>4.840000152587891</v>
+        <v>4.590000152587891</v>
       </c>
       <c r="D249" t="n">
-        <v>4.559999942779541</v>
+        <v>4.269999980926514</v>
       </c>
       <c r="E249" t="n">
-        <v>4.630000114440918</v>
+        <v>4.489999771118164</v>
       </c>
       <c r="F249" t="n">
-        <v>21375500</v>
+        <v>27151900</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>46196</v>
+        <v>46206</v>
       </c>
       <c r="B250" t="n">
-        <v>4.420000076293945</v>
+        <v>4.449999809265137</v>
       </c>
       <c r="C250" t="n">
-        <v>4.639999866485596</v>
+        <v>4.449999809265137</v>
       </c>
       <c r="D250" t="n">
-        <v>4.420000076293945</v>
+        <v>4.239999771118164</v>
       </c>
       <c r="E250" t="n">
-        <v>4.610000133514404</v>
+        <v>4.329999923706055</v>
       </c>
       <c r="F250" t="n">
-        <v>24418400</v>
+        <v>17028600</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>46197</v>
+        <v>46209</v>
       </c>
       <c r="B251" t="n">
-        <v>4.360000133514404</v>
+        <v>4.349999904632568</v>
       </c>
       <c r="C251" t="n">
-        <v>4.480000019073486</v>
+        <v>4.460000038146973</v>
       </c>
       <c r="D251" t="n">
-        <v>4.300000190734863</v>
+        <v>4.329999923706055</v>
       </c>
       <c r="E251" t="n">
-        <v>4.380000114440918</v>
+        <v>4.369999885559082</v>
       </c>
       <c r="F251" t="n">
-        <v>21608000</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="n">
-        <v>46198</v>
-      </c>
-      <c r="B252" t="n">
-        <v>4.389999866485596</v>
-      </c>
-      <c r="C252" t="n">
-        <v>4.510000228881836</v>
-      </c>
-      <c r="D252" t="n">
-        <v>4.03000020980835</v>
-      </c>
-      <c r="E252" t="n">
-        <v>4.409999847412109</v>
-      </c>
-      <c r="F252" t="n">
-        <v>51342000</v>
+        <v>12367600</v>
       </c>
     </row>
   </sheetData>
